--- a/docs/deliverables/out/Drop-1_Transactional/BRD-10_Sanction_Screening/BIBS_TestPlan_BRD-10_Sanction_Screening_v1.0.xlsx
+++ b/docs/deliverables/out/Drop-1_Transactional/BRD-10_Sanction_Screening/BIBS_TestPlan_BRD-10_Sanction_Screening_v1.0.xlsx
@@ -16,11 +16,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coverage" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Data" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roles and Access" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FRS Findings" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_lists" sheetId="11" state="hidden" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_lists" sheetId="10" state="hidden" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'README'!$A$4:$D$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'README'!$A$4:$D$65</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'README'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Document Control'!$A$4:$F$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Document Control'!$4:$4</definedName>
@@ -28,16 +27,14 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Test Conditions'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Scenarios'!$A$4:$F$12</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Scenarios'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Test Cases'!$A$4:$R$218</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Test Cases'!$A$4:$Q$218</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Test Cases'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Coverage'!$A$4:$J$90</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Coverage'!$A$4:$I$90</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Coverage'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Test Data'!$A$4:$E$14</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Test Data'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Roles and Access'!$A$4:$M$68</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Roles and Access'!$A$4:$L$68</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'Roles and Access'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'FRS Findings'!$A$4:$D$14</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="9">'FRS Findings'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -438,7 +435,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>38</row>
+      <row>37</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="971550" cy="285750"/>
@@ -751,7 +748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B4:E39"/>
+  <dimension ref="B4:E38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1010,92 +1007,77 @@
         <v>64</v>
       </c>
     </row>
-    <row r="28">
-      <c r="B28" s="11" t="inlineStr">
-        <is>
-          <t>FRS Findings</t>
-        </is>
-      </c>
-      <c r="C28" s="12" t="inlineStr">
-        <is>
-          <t>FRS points raised for the FRS owner; the affected cases assume the proposed resolution</t>
-        </is>
-      </c>
-      <c r="D28" s="12" t="n">
-        <v>10</v>
+    <row r="29">
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>Legend</t>
+        </is>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="9" t="inlineStr">
-        <is>
-          <t>Legend</t>
+      <c r="B30" s="15" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="C30" s="16" t="inlineStr">
+        <is>
+          <t>The case ran and the actual result matches the expected result</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="15" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="B31" s="17" t="inlineStr">
+        <is>
+          <t>Fail</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
         <is>
-          <t>The case ran and the actual result matches the expected result</t>
+          <t>The actual result differs; an issue ID is recorded</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="C32" s="16" t="inlineStr">
         <is>
-          <t>The actual result differs; a defect ID is recorded</t>
+          <t>The case cannot run (environment, data or an open issue elsewhere)</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="17" t="inlineStr">
-        <is>
-          <t>Blocked</t>
+      <c r="B33" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C33" s="16" t="inlineStr">
         <is>
-          <t>The case cannot run (environment, data or a defect elsewhere)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C34" s="16" t="inlineStr">
-        <is>
           <t>Not applicable in this cycle, with the reason in Actual result</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="19" t="inlineStr">
+        <is>
+          <t>Source: FRS BRD-10 Sanction Screening. 44 FRs, 42 BRD IDs, 157 test conditions, 8 scenarios, 214 test cases (99 positive, 115 negative).</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="19" t="inlineStr">
         <is>
-          <t>Source: FRS BRD-10 (FRS_BRD10_SANCTION_SCREENING.md). 44 FRs, 42 BRD IDs, 157 test conditions, 8 scenarios, 214 test cases (99 positive, 115 negative), 0 with an automation reference.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" s="19" t="inlineStr">
-        <is>
-          <t>Status starts as Not run. Testers fill Status, Actual result, Tester, Date and Defect ID during execution.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="26" customHeight="1">
-      <c r="B39" s="20" t="inlineStr">
+          <t>Status starts as Not run. Testers fill Status, Actual result, Tester, Date and Issue ID during execution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="26" customHeight="1">
+      <c r="B38" s="20" t="inlineStr">
         <is>
           <t>Prepared by iorta TechNXT for BDOI. Confidential – BDOI.</t>
         </is>
@@ -1111,7 +1093,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B27" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B28" r:id="rId9"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
@@ -1124,7 +1105,7 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId10"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9"/>
 </worksheet>
 </file>
 
@@ -1132,310 +1113,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:D14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="21" t="inlineStr">
-        <is>
-          <t>FRS Findings</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="24" t="inlineStr">
-        <is>
-          <t>FRS points raised for the FRS owner; the affected cases assume the proposed resolution</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="6" customHeight="1">
-      <c r="A3" s="25" t="n"/>
-      <c r="B3" s="25" t="n"/>
-      <c r="C3" s="25" t="n"/>
-      <c r="D3" s="25" t="n"/>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="26" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B4" s="26" t="inlineStr">
-        <is>
-          <t>FR ID</t>
-        </is>
-      </c>
-      <c r="C4" s="26" t="inlineStr">
-        <is>
-          <t>Finding</t>
-        </is>
-      </c>
-      <c r="D4" s="26" t="inlineStr">
-        <is>
-          <t>Proposed resolution</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="12" t="inlineStr">
-        <is>
-          <t>TF-SS-01</t>
-        </is>
-      </c>
-      <c r="B5" s="12" t="inlineStr">
-        <is>
-          <t>FR-SS-001</t>
-        </is>
-      </c>
-      <c r="C5" s="12" t="inlineStr">
-        <is>
-          <t>The FRS gives the no-access text as "You do not have access to this page". The platform screen shows "You do not have access to this screen. Contact your administrator if you need it." (frontend/src/auth/RequireAuth.tsx), as found for BRD-3.</t>
-        </is>
-      </c>
-      <c r="D5" s="12" t="inlineStr">
-        <is>
-          <t>Quote the platform text in FRS v1.1; the cases check the no-access page without quoting it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>TF-SS-02</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="inlineStr">
-        <is>
-          <t>FR-SS-031</t>
-        </is>
-      </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>Acceptance criterion 1 says "Juan Dela Cruz" matches "Juan de la Cruz" by the phonetic rule, but the normalisation of R4 (case, punctuation, word order) may already give an exact or fuzzy match first. The FRS does not say which algorithm is recorded when several meet their thresholds, or the expected score.</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>State the order of the algorithms and which one is recorded; give the expected algorithm and a score range for the acceptance example.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>TF-SS-03</t>
-        </is>
-      </c>
-      <c r="B7" s="12" t="inlineStr">
-        <is>
-          <t>FR-SS-034</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>The FRS says only clients with an active policy need a KYC review or EDD and others get a MONITOR case, but it does not say whether a NAME_MATCH or ACCOUNT_APPLICATION case of a client without an active policy also becomes MONITOR.</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>State the case type per trigger for clients without an active policy; the cases assume only HIGH_RISK, PEP and EDD become MONITOR.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>TF-SS-04</t>
-        </is>
-      </c>
-      <c r="B8" s="12" t="inlineStr">
-        <is>
-          <t>FR-SS-043</t>
-        </is>
-      </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>The FR names the Investigator as an actor of re-assignment, but the role matrix does not grant SCR_CASE_ASSIGN to the Investigator (SQ13).</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>Align the actor line with the matrix after SQ13; the access checks deny re-assignment to the Investigator.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>TF-SS-05</t>
-        </is>
-      </c>
-      <c r="B9" s="12" t="inlineStr">
-        <is>
-          <t>FR-SS-052</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>The naming example "KYC_REVIEW_ABC Trading_20260512_&lt;type&gt;_1" keeps a space and would keep other characters of the client name that file systems or the AMLC may refuse. The document-type code in the name is not fixed.</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>State how the client name is cleaned (spaces, punctuation, length) and which document-type value is used; the case checks the example as written.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>TF-SS-06</t>
-        </is>
-      </c>
-      <c r="B10" s="12" t="inlineStr">
-        <is>
-          <t>FR-SS-064</t>
-        </is>
-      </c>
-      <c r="C10" s="12" t="inlineStr">
-        <is>
-          <t>The FRS does not say whether MAJORITY means a majority of SCR_COMMITTEE_SIZE or of the members who hold AML_COMMITTEE, or what happens when fewer members than the size hold the role or a member is absent.</t>
-        </is>
-      </c>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>Define the quorum and the behaviour with fewer members; the cases use five members.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>TF-SS-07</t>
-        </is>
-      </c>
-      <c r="B11" s="12" t="inlineStr">
-        <is>
-          <t>FR-SS-070</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>At least one reason code is mandatory on the STR, but the list SCR_STR_REASON is delivered empty until BDOI supplies the AMLC codes (SQ09). An STR cannot be completed in UAT as delivered.</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>Deliver placeholder reason codes for testing or make the field optional until SQ09; the cases use test codes UAT01 and UAT02 added by the test lead.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="12" t="inlineStr">
-        <is>
-          <t>TF-SS-08</t>
-        </is>
-      </c>
-      <c r="B12" s="12" t="inlineStr">
-        <is>
-          <t>FR-SS-071</t>
-        </is>
-      </c>
-      <c r="C12" s="12" t="inlineStr">
-        <is>
-          <t>Acceptance criterion 1 "the committee-approved STRs of that month" does not say whether the month is the committee decision date, the STR creation date or the date the STR was marked ready.</t>
-        </is>
-      </c>
-      <c r="D12" s="12" t="inlineStr">
-        <is>
-          <t>Name the date the period filters on; the cases assume the committee decision date.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>TF-SS-09</t>
-        </is>
-      </c>
-      <c r="B13" s="12" t="inlineStr">
-        <is>
-          <t>FR-SS-018</t>
-        </is>
-      </c>
-      <c r="C13" s="12" t="inlineStr">
-        <is>
-          <t>The acceptance criterion quotes delivered values (CONCUR, NOT_CONCUR) that are placeholders until BDOI confirms the dispositions (SQ06); the test changes when the list changes.</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="inlineStr">
-        <is>
-          <t>Keep the criterion in terms of "the dispositions whose parent is the stage" and move the values to section 9.2.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="12" t="inlineStr">
-        <is>
-          <t>TF-SS-10</t>
-        </is>
-      </c>
-      <c r="B14" s="12" t="inlineStr">
-        <is>
-          <t>FR-SS-091</t>
-        </is>
-      </c>
-      <c r="C14" s="12" t="inlineStr">
-        <is>
-          <t>Acceptance criterion 2 (a database update of a timeline row is refused) needs database access that testers do not have, and the 5-year archive retention may be shorter than AMLA requires (SQ18).</t>
-        </is>
-      </c>
-      <c r="D14" s="12" t="inlineStr">
-        <is>
-          <t>Record the database check as evidence from the database administrator; confirm the retention period under SQ18.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A4:D14"/>
-  <mergeCells count="1">
-    <mergeCell ref="A2:D2"/>
-  </mergeCells>
-  <conditionalFormatting sqref="A5:D514">
-    <cfRule type="expression" priority="1" dxfId="0">
-      <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Test Plan BRD-10 Sanction Screening&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
-    <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1584,6 +1264,20 @@
       <c r="B7" t="inlineStr">
         <is>
           <t>Upload-download</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Message</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D72"/>
+  <dimension ref="A1:D65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2079,7 +1773,7 @@
       </c>
       <c r="D28" s="14" t="inlineStr">
         <is>
-          <t>Positive, Negative, Boundary, Security-access, Workflow, Report-output, Upload-download</t>
+          <t>Positive, Negative, Boundary, Security-access, Workflow, Report-output, Upload-download, Screen, Message</t>
         </is>
       </c>
     </row>
@@ -2096,7 +1790,7 @@
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Role code and name (and SIT/UAT user for built BRDs)</t>
+          <t>Role code and name (and the SIT/UAT user)</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr"/>
@@ -2168,7 +1862,7 @@
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>What the system must do, with the exact message text and, for built BRDs, its code</t>
+          <t>What the system must do, with the exact message text and, where the system shows one, its code</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr"/>
@@ -2203,15 +1897,19 @@
       </c>
       <c r="B35" s="22" t="inlineStr">
         <is>
-          <t>Automation reference</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>Existing automated test (class#method) that covers the case; blank when none</t>
-        </is>
-      </c>
-      <c r="D35" s="12" t="inlineStr"/>
+          <t>Execution status</t>
+        </is>
+      </c>
+      <c r="D35" s="12" t="inlineStr">
+        <is>
+          <t>Not run, Pass, Fail, Blocked, N/A</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="14" t="inlineStr">
@@ -2221,19 +1919,15 @@
       </c>
       <c r="B36" s="23" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Actual result</t>
         </is>
       </c>
       <c r="C36" s="14" t="inlineStr">
         <is>
-          <t>Execution status</t>
-        </is>
-      </c>
-      <c r="D36" s="14" t="inlineStr">
-        <is>
-          <t>Not run, Pass, Fail, Blocked, N/A</t>
-        </is>
-      </c>
+          <t>What happened, filled by the tester</t>
+        </is>
+      </c>
+      <c r="D36" s="14" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="12" t="inlineStr">
@@ -2243,12 +1937,12 @@
       </c>
       <c r="B37" s="22" t="inlineStr">
         <is>
-          <t>Actual result</t>
+          <t>Tester</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>What happened, filled by the tester</t>
+          <t>Who ran the case</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr"/>
@@ -2261,12 +1955,12 @@
       </c>
       <c r="B38" s="23" t="inlineStr">
         <is>
-          <t>Tester</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="C38" s="14" t="inlineStr">
         <is>
-          <t>Who ran the case</t>
+          <t>Date of the run</t>
         </is>
       </c>
       <c r="D38" s="14" t="inlineStr"/>
@@ -2279,12 +1973,12 @@
       </c>
       <c r="B39" s="22" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Issue ID</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>Date of the run</t>
+          <t>Issue raised when the case fails</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr"/>
@@ -2292,17 +1986,17 @@
     <row r="40">
       <c r="A40" s="14" t="inlineStr">
         <is>
-          <t>Test Cases</t>
+          <t>Coverage</t>
         </is>
       </c>
       <c r="B40" s="23" t="inlineStr">
         <is>
-          <t>Defect ID</t>
+          <t>FR / BRD ID</t>
         </is>
       </c>
       <c r="C40" s="14" t="inlineStr">
         <is>
-          <t>Defect raised when the case fails</t>
+          <t>FR of the FRS, then BRD requirement ID</t>
         </is>
       </c>
       <c r="D40" s="14" t="inlineStr"/>
@@ -2315,12 +2009,12 @@
       </c>
       <c r="B41" s="22" t="inlineStr">
         <is>
-          <t>FR / BRD ID</t>
+          <t>Kind</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>FR of the FRS, then BRD requirement ID</t>
+          <t>FR or BRD ID</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr"/>
@@ -2333,12 +2027,12 @@
       </c>
       <c r="B42" s="23" t="inlineStr">
         <is>
-          <t>Kind</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="C42" s="14" t="inlineStr">
         <is>
-          <t>FR or BRD ID</t>
+          <t>FR title</t>
         </is>
       </c>
       <c r="D42" s="14" t="inlineStr"/>
@@ -2351,12 +2045,12 @@
       </c>
       <c r="B43" s="22" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>Traces</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>FR title</t>
+          <t>BRD IDs of the FR, or FRs of the BRD ID</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr"/>
@@ -2369,12 +2063,12 @@
       </c>
       <c r="B44" s="23" t="inlineStr">
         <is>
-          <t>Traces</t>
+          <t>Conditions</t>
         </is>
       </c>
       <c r="C44" s="14" t="inlineStr">
         <is>
-          <t>BRD IDs of the FR, or FRs of the BRD ID</t>
+          <t>Test conditions</t>
         </is>
       </c>
       <c r="D44" s="14" t="inlineStr"/>
@@ -2387,12 +2081,12 @@
       </c>
       <c r="B45" s="22" t="inlineStr">
         <is>
-          <t>Conditions</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>Test conditions</t>
+          <t>Cases where the action succeeds</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr"/>
@@ -2405,12 +2099,12 @@
       </c>
       <c r="B46" s="23" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="C46" s="14" t="inlineStr">
         <is>
-          <t>Cases where the action succeeds</t>
+          <t>Cases where BIBS refuses the action</t>
         </is>
       </c>
       <c r="D46" s="14" t="inlineStr"/>
@@ -2423,12 +2117,12 @@
       </c>
       <c r="B47" s="22" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>Cases where BIBS refuses the action</t>
+          <t>All cases</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr"/>
@@ -2441,30 +2135,34 @@
       </c>
       <c r="B48" s="23" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Coverage</t>
         </is>
       </c>
       <c r="C48" s="14" t="inlineStr">
         <is>
-          <t>All cases</t>
-        </is>
-      </c>
-      <c r="D48" s="14" t="inlineStr"/>
+          <t>Covered: at least one positive and one negative case (FR) or one case (BRD ID); GAP otherwise</t>
+        </is>
+      </c>
+      <c r="D48" s="14" t="inlineStr">
+        <is>
+          <t>Covered, GAP</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="12" t="inlineStr">
         <is>
-          <t>Coverage</t>
+          <t>Test Data</t>
         </is>
       </c>
       <c r="B49" s="22" t="inlineStr">
         <is>
-          <t>Automated</t>
+          <t>Data set</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>Cases with an automation reference</t>
+          <t>Data set ID</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr"/>
@@ -2472,24 +2170,20 @@
     <row r="50">
       <c r="A50" s="14" t="inlineStr">
         <is>
-          <t>Coverage</t>
+          <t>Test Data</t>
         </is>
       </c>
       <c r="B50" s="23" t="inlineStr">
         <is>
-          <t>Coverage</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="C50" s="14" t="inlineStr">
         <is>
-          <t>Covered: at least one positive and one negative case (FR) or one case (BRD ID); GAP otherwise</t>
-        </is>
-      </c>
-      <c r="D50" s="14" t="inlineStr">
-        <is>
-          <t>Covered, GAP</t>
-        </is>
-      </c>
+          <t>Short name used in the cases</t>
+        </is>
+      </c>
+      <c r="D50" s="14" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
@@ -2499,12 +2193,12 @@
       </c>
       <c r="B51" s="22" t="inlineStr">
         <is>
-          <t>Data set</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>Data set ID</t>
+          <t>Records and values in the set</t>
         </is>
       </c>
       <c r="D51" s="12" t="inlineStr"/>
@@ -2517,12 +2211,12 @@
       </c>
       <c r="B52" s="23" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Source</t>
         </is>
       </c>
       <c r="C52" s="14" t="inlineStr">
         <is>
-          <t>Short name used in the cases</t>
+          <t>Seed data set that provides it, or how the tester prepares it; non-production data is masked</t>
         </is>
       </c>
       <c r="D52" s="14" t="inlineStr"/>
@@ -2535,12 +2229,12 @@
       </c>
       <c r="B53" s="22" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Cases</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>Records and values in the set</t>
+          <t>Number of cases that use it</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr"/>
@@ -2548,17 +2242,17 @@
     <row r="54">
       <c r="A54" s="14" t="inlineStr">
         <is>
-          <t>Test Data</t>
+          <t>Roles and Access</t>
         </is>
       </c>
       <c r="B54" s="23" t="inlineStr">
         <is>
-          <t>Source</t>
+          <t>Case ID</t>
         </is>
       </c>
       <c r="C54" s="14" t="inlineStr">
         <is>
-          <t>Seed that provides it (built BRDs) or how to prepare it; non-production data is masked</t>
+          <t>Access case ID: AC-&lt;code&gt;-&lt;nn&gt;.&lt;n&gt;</t>
         </is>
       </c>
       <c r="D54" s="14" t="inlineStr"/>
@@ -2566,17 +2260,17 @@
     <row r="55">
       <c r="A55" s="12" t="inlineStr">
         <is>
-          <t>Test Data</t>
+          <t>Roles and Access</t>
         </is>
       </c>
       <c r="B55" s="22" t="inlineStr">
         <is>
-          <t>Cases</t>
+          <t>Action</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>Number of cases that use it</t>
+          <t>Screen or action checked</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr"/>
@@ -2589,12 +2283,12 @@
       </c>
       <c r="B56" s="23" t="inlineStr">
         <is>
-          <t>Case ID</t>
+          <t>Screen (menu path)</t>
         </is>
       </c>
       <c r="C56" s="14" t="inlineStr">
         <is>
-          <t>Access case ID: AC-&lt;code&gt;-&lt;nn&gt;.&lt;n&gt;</t>
+          <t>Where it is done</t>
         </is>
       </c>
       <c r="D56" s="14" t="inlineStr"/>
@@ -2607,12 +2301,12 @@
       </c>
       <c r="B57" s="22" t="inlineStr">
         <is>
-          <t>Action</t>
+          <t>Permission</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>Screen or action checked</t>
+          <t>BIBS permission that grants it</t>
         </is>
       </c>
       <c r="D57" s="12" t="inlineStr"/>
@@ -2625,12 +2319,12 @@
       </c>
       <c r="B58" s="23" t="inlineStr">
         <is>
-          <t>Screen (menu path)</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="C58" s="14" t="inlineStr">
         <is>
-          <t>Where it is done</t>
+          <t>Role tested (log in as a user who holds only this role)</t>
         </is>
       </c>
       <c r="D58" s="14" t="inlineStr"/>
@@ -2643,15 +2337,19 @@
       </c>
       <c r="B59" s="22" t="inlineStr">
         <is>
-          <t>Permission</t>
+          <t>Access</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>BIBS permission that grants it</t>
-        </is>
-      </c>
-      <c r="D59" s="12" t="inlineStr"/>
+          <t>Expected access</t>
+        </is>
+      </c>
+      <c r="D59" s="12" t="inlineStr">
+        <is>
+          <t>Allowed, Denied</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="14" t="inlineStr">
@@ -2661,12 +2359,12 @@
       </c>
       <c r="B60" s="23" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>Expected result</t>
         </is>
       </c>
       <c r="C60" s="14" t="inlineStr">
         <is>
-          <t>Role tested (log in as a user who holds only this role)</t>
+          <t>What the user sees</t>
         </is>
       </c>
       <c r="D60" s="14" t="inlineStr"/>
@@ -2679,17 +2377,17 @@
       </c>
       <c r="B61" s="22" t="inlineStr">
         <is>
-          <t>Access</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>Expected access</t>
+          <t>Execution status</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>Allowed, Denied</t>
+          <t>Not run, Pass, Fail, Blocked, N/A</t>
         </is>
       </c>
     </row>
@@ -2701,12 +2399,12 @@
       </c>
       <c r="B62" s="23" t="inlineStr">
         <is>
-          <t>Expected result</t>
+          <t>Actual result</t>
         </is>
       </c>
       <c r="C62" s="14" t="inlineStr">
         <is>
-          <t>What the user sees</t>
+          <t>Filled by the tester</t>
         </is>
       </c>
       <c r="D62" s="14" t="inlineStr"/>
@@ -2719,12 +2417,12 @@
       </c>
       <c r="B63" s="22" t="inlineStr">
         <is>
-          <t>Automation reference</t>
+          <t>Tester</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>Existing automated test, if any</t>
+          <t>Who ran the case</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr"/>
@@ -2737,19 +2435,15 @@
       </c>
       <c r="B64" s="23" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="C64" s="14" t="inlineStr">
         <is>
-          <t>Execution status</t>
-        </is>
-      </c>
-      <c r="D64" s="14" t="inlineStr">
-        <is>
-          <t>Not run, Pass, Fail, Blocked, N/A</t>
-        </is>
-      </c>
+          <t>Date of the run</t>
+        </is>
+      </c>
+      <c r="D64" s="14" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="12" t="inlineStr">
@@ -2759,144 +2453,18 @@
       </c>
       <c r="B65" s="22" t="inlineStr">
         <is>
-          <t>Actual result</t>
+          <t>Issue ID</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>Filled by the tester</t>
+          <t>Issue raised when the case fails</t>
         </is>
       </c>
       <c r="D65" s="12" t="inlineStr"/>
     </row>
-    <row r="66">
-      <c r="A66" s="14" t="inlineStr">
-        <is>
-          <t>Roles and Access</t>
-        </is>
-      </c>
-      <c r="B66" s="23" t="inlineStr">
-        <is>
-          <t>Tester</t>
-        </is>
-      </c>
-      <c r="C66" s="14" t="inlineStr">
-        <is>
-          <t>Who ran the case</t>
-        </is>
-      </c>
-      <c r="D66" s="14" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="12" t="inlineStr">
-        <is>
-          <t>Roles and Access</t>
-        </is>
-      </c>
-      <c r="B67" s="22" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C67" s="12" t="inlineStr">
-        <is>
-          <t>Date of the run</t>
-        </is>
-      </c>
-      <c r="D67" s="12" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="14" t="inlineStr">
-        <is>
-          <t>Roles and Access</t>
-        </is>
-      </c>
-      <c r="B68" s="23" t="inlineStr">
-        <is>
-          <t>Defect ID</t>
-        </is>
-      </c>
-      <c r="C68" s="14" t="inlineStr">
-        <is>
-          <t>Defect raised when the case fails</t>
-        </is>
-      </c>
-      <c r="D68" s="14" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="12" t="inlineStr">
-        <is>
-          <t>FRS Findings</t>
-        </is>
-      </c>
-      <c r="B69" s="22" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="C69" s="12" t="inlineStr">
-        <is>
-          <t>Finding ID</t>
-        </is>
-      </c>
-      <c r="D69" s="12" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="14" t="inlineStr">
-        <is>
-          <t>FRS Findings</t>
-        </is>
-      </c>
-      <c r="B70" s="23" t="inlineStr">
-        <is>
-          <t>FR ID</t>
-        </is>
-      </c>
-      <c r="C70" s="14" t="inlineStr">
-        <is>
-          <t>FR concerned</t>
-        </is>
-      </c>
-      <c r="D70" s="14" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="12" t="inlineStr">
-        <is>
-          <t>FRS Findings</t>
-        </is>
-      </c>
-      <c r="B71" s="22" t="inlineStr">
-        <is>
-          <t>Finding</t>
-        </is>
-      </c>
-      <c r="C71" s="12" t="inlineStr">
-        <is>
-          <t>Ambiguous or untestable point found while writing the cases</t>
-        </is>
-      </c>
-      <c r="D71" s="12" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="14" t="inlineStr">
-        <is>
-          <t>FRS Findings</t>
-        </is>
-      </c>
-      <c r="B72" s="23" t="inlineStr">
-        <is>
-          <t>Proposed resolution</t>
-        </is>
-      </c>
-      <c r="C72" s="14" t="inlineStr">
-        <is>
-          <t>What the test team proposes to the FRS owner</t>
-        </is>
-      </c>
-      <c r="D72" s="14" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:D72"/>
+  <autoFilter ref="A4:D65"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
@@ -3006,7 +2574,7 @@
       <c r="E5" s="12" t="inlineStr"/>
       <c r="F5" s="12" t="inlineStr">
         <is>
-          <t>Internal draft from FRS BRD-10 v1.0 and the Sanction Screening build design</t>
+          <t>Internal draft from FRS BRD-10 v1.0</t>
         </is>
       </c>
     </row>
@@ -3219,7 +2787,7 @@
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>A screen or call without the permission is refused, and a refused call is logged.</t>
+          <t>A screen or direct request without the permission is refused, and a refused request is logged.</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
@@ -8531,7 +8099,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R218"/>
+  <dimension ref="A1:Q218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8546,12 +8114,11 @@
     <col width="52" customWidth="1" min="10" max="10"/>
     <col width="50" customWidth="1" min="11" max="11"/>
     <col width="9" customWidth="1" min="12" max="12"/>
-    <col width="30" customWidth="1" min="13" max="13"/>
-    <col width="11" customWidth="1" min="14" max="14"/>
-    <col width="30" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -8586,7 +8153,6 @@
       <c r="O3" s="25" t="n"/>
       <c r="P3" s="25" t="n"/>
       <c r="Q3" s="25" t="n"/>
-      <c r="R3" s="25" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="26" t="inlineStr">
@@ -8651,32 +8217,27 @@
       </c>
       <c r="M4" s="26" t="inlineStr">
         <is>
-          <t>Automation reference</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="N4" s="26" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Actual result</t>
         </is>
       </c>
       <c r="O4" s="26" t="inlineStr">
         <is>
-          <t>Actual result</t>
+          <t>Tester</t>
         </is>
       </c>
       <c r="P4" s="26" t="inlineStr">
         <is>
-          <t>Tester</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="Q4" s="26" t="inlineStr">
         <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="R4" s="26" t="inlineStr">
-        <is>
-          <t>Defect ID</t>
+          <t>Issue ID</t>
         </is>
       </c>
     </row>
@@ -8741,16 +8302,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M5" s="12" t="inlineStr"/>
-      <c r="N5" s="27" t="inlineStr">
+      <c r="M5" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N5" s="12" t="n"/>
       <c r="O5" s="12" t="n"/>
-      <c r="P5" s="12" t="n"/>
-      <c r="Q5" s="28" t="n"/>
-      <c r="R5" s="12" t="n"/>
+      <c r="P5" s="28" t="n"/>
+      <c r="Q5" s="12" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
@@ -8800,7 +8360,7 @@
       </c>
       <c r="J6" s="12" t="inlineStr">
         <is>
-          <t>1. As investigator type the address /screening-setup/config.</t>
+          <t>1. As investigator open the address of Compliance Setup directly in the browser.</t>
         </is>
       </c>
       <c r="K6" s="12" t="inlineStr">
@@ -8813,16 +8373,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M6" s="12" t="inlineStr"/>
-      <c r="N6" s="27" t="inlineStr">
+      <c r="M6" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N6" s="12" t="n"/>
       <c r="O6" s="12" t="n"/>
-      <c r="P6" s="12" t="n"/>
-      <c r="Q6" s="28" t="n"/>
-      <c r="R6" s="12" t="n"/>
+      <c r="P6" s="28" t="n"/>
+      <c r="Q6" s="12" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
@@ -8887,16 +8446,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M7" s="12" t="inlineStr"/>
-      <c r="N7" s="27" t="inlineStr">
+      <c r="M7" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N7" s="12" t="n"/>
       <c r="O7" s="12" t="n"/>
-      <c r="P7" s="12" t="n"/>
-      <c r="Q7" s="28" t="n"/>
-      <c r="R7" s="12" t="n"/>
+      <c r="P7" s="28" t="n"/>
+      <c r="Q7" s="12" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
@@ -8921,7 +8479,7 @@
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>Direct committee decision call without SCR_COMMITTEE</t>
+          <t>Direct committee decision request without SCR_COMMITTEE</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">
@@ -8936,7 +8494,7 @@
       </c>
       <c r="H8" s="12" t="inlineStr">
         <is>
-          <t>API call with the user's token (tester tool, for example Postman)</t>
+          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I8" s="12" t="inlineStr">
@@ -8946,13 +8504,13 @@
       </c>
       <c r="J8" s="12" t="inlineStr">
         <is>
-          <t>1. As investigator call Record Decision on a case in AML_COMMITTEE.
+          <t>1. As investigator send a direct request to record a committee decision on a case in AML_COMMITTEE.
 2. As auditor open Administration &gt; Audit Trail.</t>
         </is>
       </c>
       <c r="K8" s="12" t="inlineStr">
         <is>
-          <t>The call returns HTTP 403 and no vote is recorded. The refused call is logged with user, endpoint and time.
+          <t>The request is refused and no vote is recorded. The refused request is logged with the user and time.
 Message "You are not permitted to perform this action".</t>
         </is>
       </c>
@@ -8961,16 +8519,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M8" s="12" t="inlineStr"/>
-      <c r="N8" s="27" t="inlineStr">
+      <c r="M8" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N8" s="12" t="n"/>
       <c r="O8" s="12" t="n"/>
-      <c r="P8" s="12" t="n"/>
-      <c r="Q8" s="28" t="n"/>
-      <c r="R8" s="12" t="n"/>
+      <c r="P8" s="28" t="n"/>
+      <c r="Q8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
@@ -9033,16 +8590,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M9" s="12" t="inlineStr"/>
-      <c r="N9" s="27" t="inlineStr">
+      <c r="M9" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N9" s="12" t="n"/>
       <c r="O9" s="12" t="n"/>
-      <c r="P9" s="12" t="n"/>
-      <c r="Q9" s="28" t="n"/>
-      <c r="R9" s="12" t="n"/>
+      <c r="P9" s="28" t="n"/>
+      <c r="Q9" s="12" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
@@ -9105,16 +8661,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M10" s="12" t="inlineStr"/>
-      <c r="N10" s="27" t="inlineStr">
+      <c r="M10" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N10" s="12" t="n"/>
       <c r="O10" s="12" t="n"/>
-      <c r="P10" s="12" t="n"/>
-      <c r="Q10" s="28" t="n"/>
-      <c r="R10" s="12" t="n"/>
+      <c r="P10" s="28" t="n"/>
+      <c r="Q10" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
@@ -9154,7 +8709,7 @@
       </c>
       <c r="H11" s="12" t="inlineStr">
         <is>
-          <t>API call with the user's token (tester tool, for example Postman)</t>
+          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I11" s="12" t="inlineStr">
@@ -9164,7 +8719,7 @@
       </c>
       <c r="J11" s="12" t="inlineStr">
         <is>
-          <t>1. As the combined test user (SCR_INVESTIGATE) call Submit on a case in INVESTIGATION assigned to investigator.</t>
+          <t>1. As the combined test user (SCR_INVESTIGATE) send a direct request to submit a case in INVESTIGATION assigned to investigator.</t>
         </is>
       </c>
       <c r="K11" s="12" t="inlineStr">
@@ -9178,16 +8733,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M11" s="12" t="inlineStr"/>
-      <c r="N11" s="27" t="inlineStr">
+      <c r="M11" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N11" s="12" t="n"/>
       <c r="O11" s="12" t="n"/>
-      <c r="P11" s="12" t="n"/>
-      <c r="Q11" s="28" t="n"/>
-      <c r="R11" s="12" t="n"/>
+      <c r="P11" s="28" t="n"/>
+      <c r="Q11" s="12" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
@@ -9252,16 +8806,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M12" s="12" t="inlineStr"/>
-      <c r="N12" s="27" t="inlineStr">
+      <c r="M12" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N12" s="12" t="n"/>
       <c r="O12" s="12" t="n"/>
-      <c r="P12" s="12" t="n"/>
-      <c r="Q12" s="28" t="n"/>
-      <c r="R12" s="12" t="n"/>
+      <c r="P12" s="28" t="n"/>
+      <c r="Q12" s="12" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
@@ -9324,16 +8877,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M13" s="12" t="inlineStr"/>
-      <c r="N13" s="27" t="inlineStr">
+      <c r="M13" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N13" s="12" t="n"/>
       <c r="O13" s="12" t="n"/>
-      <c r="P13" s="12" t="n"/>
-      <c r="Q13" s="28" t="n"/>
-      <c r="R13" s="12" t="n"/>
+      <c r="P13" s="28" t="n"/>
+      <c r="Q13" s="12" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
@@ -9397,16 +8949,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M14" s="12" t="inlineStr"/>
-      <c r="N14" s="27" t="inlineStr">
+      <c r="M14" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N14" s="12" t="n"/>
       <c r="O14" s="12" t="n"/>
-      <c r="P14" s="12" t="n"/>
-      <c r="Q14" s="28" t="n"/>
-      <c r="R14" s="12" t="n"/>
+      <c r="P14" s="28" t="n"/>
+      <c r="Q14" s="12" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
@@ -9470,16 +9021,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M15" s="12" t="inlineStr"/>
-      <c r="N15" s="27" t="inlineStr">
+      <c r="M15" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N15" s="12" t="n"/>
       <c r="O15" s="12" t="n"/>
-      <c r="P15" s="12" t="n"/>
-      <c r="Q15" s="28" t="n"/>
-      <c r="R15" s="12" t="n"/>
+      <c r="P15" s="28" t="n"/>
+      <c r="Q15" s="12" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
@@ -9542,16 +9092,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M16" s="12" t="inlineStr"/>
-      <c r="N16" s="27" t="inlineStr">
+      <c r="M16" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N16" s="12" t="n"/>
       <c r="O16" s="12" t="n"/>
-      <c r="P16" s="12" t="n"/>
-      <c r="Q16" s="28" t="n"/>
-      <c r="R16" s="12" t="n"/>
+      <c r="P16" s="28" t="n"/>
+      <c r="Q16" s="12" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
@@ -9615,16 +9164,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M17" s="12" t="inlineStr"/>
-      <c r="N17" s="27" t="inlineStr">
+      <c r="M17" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N17" s="12" t="n"/>
       <c r="O17" s="12" t="n"/>
-      <c r="P17" s="12" t="n"/>
-      <c r="Q17" s="28" t="n"/>
-      <c r="R17" s="12" t="n"/>
+      <c r="P17" s="28" t="n"/>
+      <c r="Q17" s="12" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
@@ -9688,16 +9236,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M18" s="12" t="inlineStr"/>
-      <c r="N18" s="27" t="inlineStr">
+      <c r="M18" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N18" s="12" t="n"/>
       <c r="O18" s="12" t="n"/>
-      <c r="P18" s="12" t="n"/>
-      <c r="Q18" s="28" t="n"/>
-      <c r="R18" s="12" t="n"/>
+      <c r="P18" s="28" t="n"/>
+      <c r="Q18" s="12" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
@@ -9762,16 +9309,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M19" s="12" t="inlineStr"/>
-      <c r="N19" s="27" t="inlineStr">
+      <c r="M19" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N19" s="12" t="n"/>
       <c r="O19" s="12" t="n"/>
-      <c r="P19" s="12" t="n"/>
-      <c r="Q19" s="28" t="n"/>
-      <c r="R19" s="12" t="n"/>
+      <c r="P19" s="28" t="n"/>
+      <c r="Q19" s="12" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
@@ -9834,16 +9380,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M20" s="12" t="inlineStr"/>
-      <c r="N20" s="27" t="inlineStr">
+      <c r="M20" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N20" s="12" t="n"/>
       <c r="O20" s="12" t="n"/>
-      <c r="P20" s="12" t="n"/>
-      <c r="Q20" s="28" t="n"/>
-      <c r="R20" s="12" t="n"/>
+      <c r="P20" s="28" t="n"/>
+      <c r="Q20" s="12" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
@@ -9908,16 +9453,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M21" s="12" t="inlineStr"/>
-      <c r="N21" s="27" t="inlineStr">
+      <c r="M21" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N21" s="12" t="n"/>
       <c r="O21" s="12" t="n"/>
-      <c r="P21" s="12" t="n"/>
-      <c r="Q21" s="28" t="n"/>
-      <c r="R21" s="12" t="n"/>
+      <c r="P21" s="28" t="n"/>
+      <c r="Q21" s="12" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
@@ -9981,16 +9525,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M22" s="12" t="inlineStr"/>
-      <c r="N22" s="27" t="inlineStr">
+      <c r="M22" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N22" s="12" t="n"/>
       <c r="O22" s="12" t="n"/>
-      <c r="P22" s="12" t="n"/>
-      <c r="Q22" s="28" t="n"/>
-      <c r="R22" s="12" t="n"/>
+      <c r="P22" s="28" t="n"/>
+      <c r="Q22" s="12" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
@@ -10053,16 +9596,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M23" s="12" t="inlineStr"/>
-      <c r="N23" s="27" t="inlineStr">
+      <c r="M23" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N23" s="12" t="n"/>
       <c r="O23" s="12" t="n"/>
-      <c r="P23" s="12" t="n"/>
-      <c r="Q23" s="28" t="n"/>
-      <c r="R23" s="12" t="n"/>
+      <c r="P23" s="28" t="n"/>
+      <c r="Q23" s="12" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
@@ -10126,16 +9668,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M24" s="12" t="inlineStr"/>
-      <c r="N24" s="27" t="inlineStr">
+      <c r="M24" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N24" s="12" t="n"/>
       <c r="O24" s="12" t="n"/>
-      <c r="P24" s="12" t="n"/>
-      <c r="Q24" s="28" t="n"/>
-      <c r="R24" s="12" t="n"/>
+      <c r="P24" s="28" t="n"/>
+      <c r="Q24" s="12" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
@@ -10199,16 +9740,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M25" s="12" t="inlineStr"/>
-      <c r="N25" s="27" t="inlineStr">
+      <c r="M25" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N25" s="12" t="n"/>
       <c r="O25" s="12" t="n"/>
-      <c r="P25" s="12" t="n"/>
-      <c r="Q25" s="28" t="n"/>
-      <c r="R25" s="12" t="n"/>
+      <c r="P25" s="28" t="n"/>
+      <c r="Q25" s="12" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
@@ -10273,16 +9813,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M26" s="12" t="inlineStr"/>
-      <c r="N26" s="27" t="inlineStr">
+      <c r="M26" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N26" s="12" t="n"/>
       <c r="O26" s="12" t="n"/>
-      <c r="P26" s="12" t="n"/>
-      <c r="Q26" s="28" t="n"/>
-      <c r="R26" s="12" t="n"/>
+      <c r="P26" s="28" t="n"/>
+      <c r="Q26" s="12" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
@@ -10346,16 +9885,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M27" s="12" t="inlineStr"/>
-      <c r="N27" s="27" t="inlineStr">
+      <c r="M27" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N27" s="12" t="n"/>
       <c r="O27" s="12" t="n"/>
-      <c r="P27" s="12" t="n"/>
-      <c r="Q27" s="28" t="n"/>
-      <c r="R27" s="12" t="n"/>
+      <c r="P27" s="28" t="n"/>
+      <c r="Q27" s="12" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
@@ -10419,16 +9957,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M28" s="12" t="inlineStr"/>
-      <c r="N28" s="27" t="inlineStr">
+      <c r="M28" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N28" s="12" t="n"/>
       <c r="O28" s="12" t="n"/>
-      <c r="P28" s="12" t="n"/>
-      <c r="Q28" s="28" t="n"/>
-      <c r="R28" s="12" t="n"/>
+      <c r="P28" s="28" t="n"/>
+      <c r="Q28" s="12" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
@@ -10492,16 +10029,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M29" s="12" t="inlineStr"/>
-      <c r="N29" s="27" t="inlineStr">
+      <c r="M29" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N29" s="12" t="n"/>
       <c r="O29" s="12" t="n"/>
-      <c r="P29" s="12" t="n"/>
-      <c r="Q29" s="28" t="n"/>
-      <c r="R29" s="12" t="n"/>
+      <c r="P29" s="28" t="n"/>
+      <c r="Q29" s="12" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
@@ -10565,16 +10101,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M30" s="12" t="inlineStr"/>
-      <c r="N30" s="27" t="inlineStr">
+      <c r="M30" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N30" s="12" t="n"/>
       <c r="O30" s="12" t="n"/>
-      <c r="P30" s="12" t="n"/>
-      <c r="Q30" s="28" t="n"/>
-      <c r="R30" s="12" t="n"/>
+      <c r="P30" s="28" t="n"/>
+      <c r="Q30" s="12" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
@@ -10639,16 +10174,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M31" s="12" t="inlineStr"/>
-      <c r="N31" s="27" t="inlineStr">
+      <c r="M31" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N31" s="12" t="n"/>
       <c r="O31" s="12" t="n"/>
-      <c r="P31" s="12" t="n"/>
-      <c r="Q31" s="28" t="n"/>
-      <c r="R31" s="12" t="n"/>
+      <c r="P31" s="28" t="n"/>
+      <c r="Q31" s="12" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
@@ -10711,16 +10245,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M32" s="12" t="inlineStr"/>
-      <c r="N32" s="27" t="inlineStr">
+      <c r="M32" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N32" s="12" t="n"/>
       <c r="O32" s="12" t="n"/>
-      <c r="P32" s="12" t="n"/>
-      <c r="Q32" s="28" t="n"/>
-      <c r="R32" s="12" t="n"/>
+      <c r="P32" s="28" t="n"/>
+      <c r="Q32" s="12" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
@@ -10784,16 +10317,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M33" s="12" t="inlineStr"/>
-      <c r="N33" s="27" t="inlineStr">
+      <c r="M33" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N33" s="12" t="n"/>
       <c r="O33" s="12" t="n"/>
-      <c r="P33" s="12" t="n"/>
-      <c r="Q33" s="28" t="n"/>
-      <c r="R33" s="12" t="n"/>
+      <c r="P33" s="28" t="n"/>
+      <c r="Q33" s="12" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
@@ -10857,16 +10389,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M34" s="12" t="inlineStr"/>
-      <c r="N34" s="27" t="inlineStr">
+      <c r="M34" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N34" s="12" t="n"/>
       <c r="O34" s="12" t="n"/>
-      <c r="P34" s="12" t="n"/>
-      <c r="Q34" s="28" t="n"/>
-      <c r="R34" s="12" t="n"/>
+      <c r="P34" s="28" t="n"/>
+      <c r="Q34" s="12" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
@@ -10930,16 +10461,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M35" s="12" t="inlineStr"/>
-      <c r="N35" s="27" t="inlineStr">
+      <c r="M35" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N35" s="12" t="n"/>
       <c r="O35" s="12" t="n"/>
-      <c r="P35" s="12" t="n"/>
-      <c r="Q35" s="28" t="n"/>
-      <c r="R35" s="12" t="n"/>
+      <c r="P35" s="28" t="n"/>
+      <c r="Q35" s="12" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
@@ -11003,16 +10533,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M36" s="12" t="inlineStr"/>
-      <c r="N36" s="27" t="inlineStr">
+      <c r="M36" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N36" s="12" t="n"/>
       <c r="O36" s="12" t="n"/>
-      <c r="P36" s="12" t="n"/>
-      <c r="Q36" s="28" t="n"/>
-      <c r="R36" s="12" t="n"/>
+      <c r="P36" s="28" t="n"/>
+      <c r="Q36" s="12" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="12" t="inlineStr">
@@ -11076,16 +10605,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M37" s="12" t="inlineStr"/>
-      <c r="N37" s="27" t="inlineStr">
+      <c r="M37" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N37" s="12" t="n"/>
       <c r="O37" s="12" t="n"/>
-      <c r="P37" s="12" t="n"/>
-      <c r="Q37" s="28" t="n"/>
-      <c r="R37" s="12" t="n"/>
+      <c r="P37" s="28" t="n"/>
+      <c r="Q37" s="12" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="12" t="inlineStr">
@@ -11149,16 +10677,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M38" s="12" t="inlineStr"/>
-      <c r="N38" s="27" t="inlineStr">
+      <c r="M38" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N38" s="12" t="n"/>
       <c r="O38" s="12" t="n"/>
-      <c r="P38" s="12" t="n"/>
-      <c r="Q38" s="28" t="n"/>
-      <c r="R38" s="12" t="n"/>
+      <c r="P38" s="28" t="n"/>
+      <c r="Q38" s="12" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="12" t="inlineStr">
@@ -11222,16 +10749,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M39" s="12" t="inlineStr"/>
-      <c r="N39" s="27" t="inlineStr">
+      <c r="M39" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N39" s="12" t="n"/>
       <c r="O39" s="12" t="n"/>
-      <c r="P39" s="12" t="n"/>
-      <c r="Q39" s="28" t="n"/>
-      <c r="R39" s="12" t="n"/>
+      <c r="P39" s="28" t="n"/>
+      <c r="Q39" s="12" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="12" t="inlineStr">
@@ -11294,16 +10820,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M40" s="12" t="inlineStr"/>
-      <c r="N40" s="27" t="inlineStr">
+      <c r="M40" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N40" s="12" t="n"/>
       <c r="O40" s="12" t="n"/>
-      <c r="P40" s="12" t="n"/>
-      <c r="Q40" s="28" t="n"/>
-      <c r="R40" s="12" t="n"/>
+      <c r="P40" s="28" t="n"/>
+      <c r="Q40" s="12" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
@@ -11366,16 +10891,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M41" s="12" t="inlineStr"/>
-      <c r="N41" s="27" t="inlineStr">
+      <c r="M41" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N41" s="12" t="n"/>
       <c r="O41" s="12" t="n"/>
-      <c r="P41" s="12" t="n"/>
-      <c r="Q41" s="28" t="n"/>
-      <c r="R41" s="12" t="n"/>
+      <c r="P41" s="28" t="n"/>
+      <c r="Q41" s="12" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="12" t="inlineStr">
@@ -11439,16 +10963,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M42" s="12" t="inlineStr"/>
-      <c r="N42" s="27" t="inlineStr">
+      <c r="M42" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N42" s="12" t="n"/>
       <c r="O42" s="12" t="n"/>
-      <c r="P42" s="12" t="n"/>
-      <c r="Q42" s="28" t="n"/>
-      <c r="R42" s="12" t="n"/>
+      <c r="P42" s="28" t="n"/>
+      <c r="Q42" s="12" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="12" t="inlineStr">
@@ -11512,16 +11035,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M43" s="12" t="inlineStr"/>
-      <c r="N43" s="27" t="inlineStr">
+      <c r="M43" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N43" s="12" t="n"/>
       <c r="O43" s="12" t="n"/>
-      <c r="P43" s="12" t="n"/>
-      <c r="Q43" s="28" t="n"/>
-      <c r="R43" s="12" t="n"/>
+      <c r="P43" s="28" t="n"/>
+      <c r="Q43" s="12" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="12" t="inlineStr">
@@ -11585,16 +11107,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M44" s="12" t="inlineStr"/>
-      <c r="N44" s="27" t="inlineStr">
+      <c r="M44" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N44" s="12" t="n"/>
       <c r="O44" s="12" t="n"/>
-      <c r="P44" s="12" t="n"/>
-      <c r="Q44" s="28" t="n"/>
-      <c r="R44" s="12" t="n"/>
+      <c r="P44" s="28" t="n"/>
+      <c r="Q44" s="12" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="12" t="inlineStr">
@@ -11659,16 +11180,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M45" s="12" t="inlineStr"/>
-      <c r="N45" s="27" t="inlineStr">
+      <c r="M45" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N45" s="12" t="n"/>
       <c r="O45" s="12" t="n"/>
-      <c r="P45" s="12" t="n"/>
-      <c r="Q45" s="28" t="n"/>
-      <c r="R45" s="12" t="n"/>
+      <c r="P45" s="28" t="n"/>
+      <c r="Q45" s="12" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="12" t="inlineStr">
@@ -11732,16 +11252,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M46" s="12" t="inlineStr"/>
-      <c r="N46" s="27" t="inlineStr">
+      <c r="M46" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N46" s="12" t="n"/>
       <c r="O46" s="12" t="n"/>
-      <c r="P46" s="12" t="n"/>
-      <c r="Q46" s="28" t="n"/>
-      <c r="R46" s="12" t="n"/>
+      <c r="P46" s="28" t="n"/>
+      <c r="Q46" s="12" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="12" t="inlineStr">
@@ -11805,16 +11324,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M47" s="12" t="inlineStr"/>
-      <c r="N47" s="27" t="inlineStr">
+      <c r="M47" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N47" s="12" t="n"/>
       <c r="O47" s="12" t="n"/>
-      <c r="P47" s="12" t="n"/>
-      <c r="Q47" s="28" t="n"/>
-      <c r="R47" s="12" t="n"/>
+      <c r="P47" s="28" t="n"/>
+      <c r="Q47" s="12" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="12" t="inlineStr">
@@ -11878,16 +11396,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M48" s="12" t="inlineStr"/>
-      <c r="N48" s="27" t="inlineStr">
+      <c r="M48" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N48" s="12" t="n"/>
       <c r="O48" s="12" t="n"/>
-      <c r="P48" s="12" t="n"/>
-      <c r="Q48" s="28" t="n"/>
-      <c r="R48" s="12" t="n"/>
+      <c r="P48" s="28" t="n"/>
+      <c r="Q48" s="12" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="12" t="inlineStr">
@@ -11951,16 +11468,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M49" s="12" t="inlineStr"/>
-      <c r="N49" s="27" t="inlineStr">
+      <c r="M49" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N49" s="12" t="n"/>
       <c r="O49" s="12" t="n"/>
-      <c r="P49" s="12" t="n"/>
-      <c r="Q49" s="28" t="n"/>
-      <c r="R49" s="12" t="n"/>
+      <c r="P49" s="28" t="n"/>
+      <c r="Q49" s="12" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="12" t="inlineStr">
@@ -12023,16 +11539,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M50" s="12" t="inlineStr"/>
-      <c r="N50" s="27" t="inlineStr">
+      <c r="M50" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N50" s="12" t="n"/>
       <c r="O50" s="12" t="n"/>
-      <c r="P50" s="12" t="n"/>
-      <c r="Q50" s="28" t="n"/>
-      <c r="R50" s="12" t="n"/>
+      <c r="P50" s="28" t="n"/>
+      <c r="Q50" s="12" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
@@ -12097,16 +11612,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M51" s="12" t="inlineStr"/>
-      <c r="N51" s="27" t="inlineStr">
+      <c r="M51" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N51" s="12" t="n"/>
       <c r="O51" s="12" t="n"/>
-      <c r="P51" s="12" t="n"/>
-      <c r="Q51" s="28" t="n"/>
-      <c r="R51" s="12" t="n"/>
+      <c r="P51" s="28" t="n"/>
+      <c r="Q51" s="12" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="12" t="inlineStr">
@@ -12170,16 +11684,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M52" s="12" t="inlineStr"/>
-      <c r="N52" s="27" t="inlineStr">
+      <c r="M52" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N52" s="12" t="n"/>
       <c r="O52" s="12" t="n"/>
-      <c r="P52" s="12" t="n"/>
-      <c r="Q52" s="28" t="n"/>
-      <c r="R52" s="12" t="n"/>
+      <c r="P52" s="28" t="n"/>
+      <c r="Q52" s="12" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="12" t="inlineStr">
@@ -12243,16 +11756,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M53" s="12" t="inlineStr"/>
-      <c r="N53" s="27" t="inlineStr">
+      <c r="M53" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N53" s="12" t="n"/>
       <c r="O53" s="12" t="n"/>
-      <c r="P53" s="12" t="n"/>
-      <c r="Q53" s="28" t="n"/>
-      <c r="R53" s="12" t="n"/>
+      <c r="P53" s="28" t="n"/>
+      <c r="Q53" s="12" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="12" t="inlineStr">
@@ -12316,16 +11828,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M54" s="12" t="inlineStr"/>
-      <c r="N54" s="27" t="inlineStr">
+      <c r="M54" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N54" s="12" t="n"/>
       <c r="O54" s="12" t="n"/>
-      <c r="P54" s="12" t="n"/>
-      <c r="Q54" s="28" t="n"/>
-      <c r="R54" s="12" t="n"/>
+      <c r="P54" s="28" t="n"/>
+      <c r="Q54" s="12" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="12" t="inlineStr">
@@ -12389,16 +11900,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M55" s="12" t="inlineStr"/>
-      <c r="N55" s="27" t="inlineStr">
+      <c r="M55" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N55" s="12" t="n"/>
       <c r="O55" s="12" t="n"/>
-      <c r="P55" s="12" t="n"/>
-      <c r="Q55" s="28" t="n"/>
-      <c r="R55" s="12" t="n"/>
+      <c r="P55" s="28" t="n"/>
+      <c r="Q55" s="12" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="12" t="inlineStr">
@@ -12462,16 +11972,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M56" s="12" t="inlineStr"/>
-      <c r="N56" s="27" t="inlineStr">
+      <c r="M56" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N56" s="12" t="n"/>
       <c r="O56" s="12" t="n"/>
-      <c r="P56" s="12" t="n"/>
-      <c r="Q56" s="28" t="n"/>
-      <c r="R56" s="12" t="n"/>
+      <c r="P56" s="28" t="n"/>
+      <c r="Q56" s="12" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="12" t="inlineStr">
@@ -12535,16 +12044,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M57" s="12" t="inlineStr"/>
-      <c r="N57" s="27" t="inlineStr">
+      <c r="M57" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N57" s="12" t="n"/>
       <c r="O57" s="12" t="n"/>
-      <c r="P57" s="12" t="n"/>
-      <c r="Q57" s="28" t="n"/>
-      <c r="R57" s="12" t="n"/>
+      <c r="P57" s="28" t="n"/>
+      <c r="Q57" s="12" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="12" t="inlineStr">
@@ -12608,16 +12116,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M58" s="12" t="inlineStr"/>
-      <c r="N58" s="27" t="inlineStr">
+      <c r="M58" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N58" s="12" t="n"/>
       <c r="O58" s="12" t="n"/>
-      <c r="P58" s="12" t="n"/>
-      <c r="Q58" s="28" t="n"/>
-      <c r="R58" s="12" t="n"/>
+      <c r="P58" s="28" t="n"/>
+      <c r="Q58" s="12" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="12" t="inlineStr">
@@ -12681,16 +12188,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M59" s="12" t="inlineStr"/>
-      <c r="N59" s="27" t="inlineStr">
+      <c r="M59" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N59" s="12" t="n"/>
       <c r="O59" s="12" t="n"/>
-      <c r="P59" s="12" t="n"/>
-      <c r="Q59" s="28" t="n"/>
-      <c r="R59" s="12" t="n"/>
+      <c r="P59" s="28" t="n"/>
+      <c r="Q59" s="12" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="12" t="inlineStr">
@@ -12753,16 +12259,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M60" s="12" t="inlineStr"/>
-      <c r="N60" s="27" t="inlineStr">
+      <c r="M60" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N60" s="12" t="n"/>
       <c r="O60" s="12" t="n"/>
-      <c r="P60" s="12" t="n"/>
-      <c r="Q60" s="28" t="n"/>
-      <c r="R60" s="12" t="n"/>
+      <c r="P60" s="28" t="n"/>
+      <c r="Q60" s="12" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="12" t="inlineStr">
@@ -12802,7 +12307,7 @@
       </c>
       <c r="H61" s="12" t="inlineStr">
         <is>
-          <t>API call with the user's token (tester tool, for example Postman)</t>
+          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I61" s="12" t="inlineStr">
@@ -12812,7 +12317,7 @@
       </c>
       <c r="J61" s="12" t="inlineStr">
         <is>
-          <t>1. As investigator submit a case in INVESTIGATION with disposition CONCUR through the API.</t>
+          <t>1. As investigator submit a case in INVESTIGATION with disposition CONCUR by a direct request.</t>
         </is>
       </c>
       <c r="K61" s="12" t="inlineStr">
@@ -12826,16 +12331,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M61" s="12" t="inlineStr"/>
-      <c r="N61" s="27" t="inlineStr">
+      <c r="M61" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N61" s="12" t="n"/>
       <c r="O61" s="12" t="n"/>
-      <c r="P61" s="12" t="n"/>
-      <c r="Q61" s="28" t="n"/>
-      <c r="R61" s="12" t="n"/>
+      <c r="P61" s="28" t="n"/>
+      <c r="Q61" s="12" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="12" t="inlineStr">
@@ -12899,16 +12403,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M62" s="12" t="inlineStr"/>
-      <c r="N62" s="27" t="inlineStr">
+      <c r="M62" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N62" s="12" t="n"/>
       <c r="O62" s="12" t="n"/>
-      <c r="P62" s="12" t="n"/>
-      <c r="Q62" s="28" t="n"/>
-      <c r="R62" s="12" t="n"/>
+      <c r="P62" s="28" t="n"/>
+      <c r="Q62" s="12" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="12" t="inlineStr">
@@ -12972,16 +12475,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M63" s="12" t="inlineStr"/>
-      <c r="N63" s="27" t="inlineStr">
+      <c r="M63" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N63" s="12" t="n"/>
       <c r="O63" s="12" t="n"/>
-      <c r="P63" s="12" t="n"/>
-      <c r="Q63" s="28" t="n"/>
-      <c r="R63" s="12" t="n"/>
+      <c r="P63" s="28" t="n"/>
+      <c r="Q63" s="12" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="12" t="inlineStr">
@@ -13044,16 +12546,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M64" s="12" t="inlineStr"/>
-      <c r="N64" s="27" t="inlineStr">
+      <c r="M64" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N64" s="12" t="n"/>
       <c r="O64" s="12" t="n"/>
-      <c r="P64" s="12" t="n"/>
-      <c r="Q64" s="28" t="n"/>
-      <c r="R64" s="12" t="n"/>
+      <c r="P64" s="28" t="n"/>
+      <c r="Q64" s="12" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="12" t="inlineStr">
@@ -13117,16 +12618,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M65" s="12" t="inlineStr"/>
-      <c r="N65" s="27" t="inlineStr">
+      <c r="M65" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N65" s="12" t="n"/>
       <c r="O65" s="12" t="n"/>
-      <c r="P65" s="12" t="n"/>
-      <c r="Q65" s="28" t="n"/>
-      <c r="R65" s="12" t="n"/>
+      <c r="P65" s="28" t="n"/>
+      <c r="Q65" s="12" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="12" t="inlineStr">
@@ -13189,16 +12689,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M66" s="12" t="inlineStr"/>
-      <c r="N66" s="27" t="inlineStr">
+      <c r="M66" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N66" s="12" t="n"/>
       <c r="O66" s="12" t="n"/>
-      <c r="P66" s="12" t="n"/>
-      <c r="Q66" s="28" t="n"/>
-      <c r="R66" s="12" t="n"/>
+      <c r="P66" s="28" t="n"/>
+      <c r="Q66" s="12" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="12" t="inlineStr">
@@ -13262,16 +12761,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M67" s="12" t="inlineStr"/>
-      <c r="N67" s="27" t="inlineStr">
+      <c r="M67" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N67" s="12" t="n"/>
       <c r="O67" s="12" t="n"/>
-      <c r="P67" s="12" t="n"/>
-      <c r="Q67" s="28" t="n"/>
-      <c r="R67" s="12" t="n"/>
+      <c r="P67" s="28" t="n"/>
+      <c r="Q67" s="12" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="12" t="inlineStr">
@@ -13336,16 +12834,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M68" s="12" t="inlineStr"/>
-      <c r="N68" s="27" t="inlineStr">
+      <c r="M68" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N68" s="12" t="n"/>
       <c r="O68" s="12" t="n"/>
-      <c r="P68" s="12" t="n"/>
-      <c r="Q68" s="28" t="n"/>
-      <c r="R68" s="12" t="n"/>
+      <c r="P68" s="28" t="n"/>
+      <c r="Q68" s="12" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="12" t="inlineStr">
@@ -13409,16 +12906,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M69" s="12" t="inlineStr"/>
-      <c r="N69" s="27" t="inlineStr">
+      <c r="M69" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N69" s="12" t="n"/>
       <c r="O69" s="12" t="n"/>
-      <c r="P69" s="12" t="n"/>
-      <c r="Q69" s="28" t="n"/>
-      <c r="R69" s="12" t="n"/>
+      <c r="P69" s="28" t="n"/>
+      <c r="Q69" s="12" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="12" t="inlineStr">
@@ -13464,7 +12960,7 @@
       <c r="I70" s="12" t="inlineStr">
         <is>
           <t>The AML_ADVISORY file of TD-SS-04 (3 new, 1 changed) is in the source location.
-Data: TD-SS-03 Watchlist with invented names; TD-SS-04 List files; TD-SS-10 Parameters and jobs as delivered</t>
+Data: TD-SS-03 Watchlist with invented names; TD-SS-04 List files; TD-SS-10 Parameters and jobs at their defaults</t>
         </is>
       </c>
       <c r="J70" s="12" t="inlineStr">
@@ -13483,16 +12979,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M70" s="12" t="inlineStr"/>
-      <c r="N70" s="27" t="inlineStr">
+      <c r="M70" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N70" s="12" t="n"/>
       <c r="O70" s="12" t="n"/>
-      <c r="P70" s="12" t="n"/>
-      <c r="Q70" s="28" t="n"/>
-      <c r="R70" s="12" t="n"/>
+      <c r="P70" s="28" t="n"/>
+      <c r="Q70" s="12" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="12" t="inlineStr">
@@ -13537,7 +13032,7 @@
       </c>
       <c r="I71" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-SS-03 Watchlist with invented names; TD-SS-04 List files; TD-SS-10 Parameters and jobs as delivered</t>
+          <t>Data: TD-SS-03 Watchlist with invented names; TD-SS-04 List files; TD-SS-10 Parameters and jobs at their defaults</t>
         </is>
       </c>
       <c r="J71" s="12" t="inlineStr">
@@ -13555,16 +13050,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M71" s="12" t="inlineStr"/>
-      <c r="N71" s="27" t="inlineStr">
+      <c r="M71" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N71" s="12" t="n"/>
       <c r="O71" s="12" t="n"/>
-      <c r="P71" s="12" t="n"/>
-      <c r="Q71" s="28" t="n"/>
-      <c r="R71" s="12" t="n"/>
+      <c r="P71" s="28" t="n"/>
+      <c r="Q71" s="12" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="12" t="inlineStr">
@@ -13609,7 +13103,7 @@
       </c>
       <c r="I72" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-SS-03 Watchlist with invented names; TD-SS-04 List files; TD-SS-10 Parameters and jobs as delivered</t>
+          <t>Data: TD-SS-03 Watchlist with invented names; TD-SS-04 List files; TD-SS-10 Parameters and jobs at their defaults</t>
         </is>
       </c>
       <c r="J72" s="12" t="inlineStr">
@@ -13628,16 +13122,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M72" s="12" t="inlineStr"/>
-      <c r="N72" s="27" t="inlineStr">
+      <c r="M72" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N72" s="12" t="n"/>
       <c r="O72" s="12" t="n"/>
-      <c r="P72" s="12" t="n"/>
-      <c r="Q72" s="28" t="n"/>
-      <c r="R72" s="12" t="n"/>
+      <c r="P72" s="28" t="n"/>
+      <c r="Q72" s="12" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="12" t="inlineStr">
@@ -13682,7 +13175,7 @@
       </c>
       <c r="I73" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-SS-03 Watchlist with invented names; TD-SS-04 List files; TD-SS-10 Parameters and jobs as delivered</t>
+          <t>Data: TD-SS-03 Watchlist with invented names; TD-SS-04 List files; TD-SS-10 Parameters and jobs at their defaults</t>
         </is>
       </c>
       <c r="J73" s="12" t="inlineStr">
@@ -13700,16 +13193,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M73" s="12" t="inlineStr"/>
-      <c r="N73" s="27" t="inlineStr">
+      <c r="M73" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N73" s="12" t="n"/>
       <c r="O73" s="12" t="n"/>
-      <c r="P73" s="12" t="n"/>
-      <c r="Q73" s="28" t="n"/>
-      <c r="R73" s="12" t="n"/>
+      <c r="P73" s="28" t="n"/>
+      <c r="Q73" s="12" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="12" t="inlineStr">
@@ -13754,7 +13246,7 @@
       </c>
       <c r="I74" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-SS-03 Watchlist with invented names; TD-SS-04 List files; TD-SS-10 Parameters and jobs as delivered</t>
+          <t>Data: TD-SS-03 Watchlist with invented names; TD-SS-04 List files; TD-SS-10 Parameters and jobs at their defaults</t>
         </is>
       </c>
       <c r="J74" s="12" t="inlineStr">
@@ -13773,16 +13265,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M74" s="12" t="inlineStr"/>
-      <c r="N74" s="27" t="inlineStr">
+      <c r="M74" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N74" s="12" t="n"/>
       <c r="O74" s="12" t="n"/>
-      <c r="P74" s="12" t="n"/>
-      <c r="Q74" s="28" t="n"/>
-      <c r="R74" s="12" t="n"/>
+      <c r="P74" s="28" t="n"/>
+      <c r="Q74" s="12" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="12" t="inlineStr">
@@ -13828,7 +13319,7 @@
       <c r="I75" s="12" t="inlineStr">
         <is>
           <t>The next AML_ADVISORY file omits one active entry.
-Data: TD-SS-03 Watchlist with invented names; TD-SS-04 List files; TD-SS-10 Parameters and jobs as delivered</t>
+Data: TD-SS-03 Watchlist with invented names; TD-SS-04 List files; TD-SS-10 Parameters and jobs at their defaults</t>
         </is>
       </c>
       <c r="J75" s="12" t="inlineStr">
@@ -13846,16 +13337,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M75" s="12" t="inlineStr"/>
-      <c r="N75" s="27" t="inlineStr">
+      <c r="M75" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N75" s="12" t="n"/>
       <c r="O75" s="12" t="n"/>
-      <c r="P75" s="12" t="n"/>
-      <c r="Q75" s="28" t="n"/>
-      <c r="R75" s="12" t="n"/>
+      <c r="P75" s="28" t="n"/>
+      <c r="Q75" s="12" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="12" t="inlineStr">
@@ -13900,7 +13390,7 @@
       </c>
       <c r="I76" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-SS-04 List files; TD-SS-10 Parameters and jobs as delivered</t>
+          <t>Data: TD-SS-04 List files; TD-SS-10 Parameters and jobs at their defaults</t>
         </is>
       </c>
       <c r="J76" s="12" t="inlineStr">
@@ -13919,16 +13409,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M76" s="12" t="inlineStr"/>
-      <c r="N76" s="27" t="inlineStr">
+      <c r="M76" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N76" s="12" t="n"/>
       <c r="O76" s="12" t="n"/>
-      <c r="P76" s="12" t="n"/>
-      <c r="Q76" s="28" t="n"/>
-      <c r="R76" s="12" t="n"/>
+      <c r="P76" s="28" t="n"/>
+      <c r="Q76" s="12" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="12" t="inlineStr">
@@ -13973,7 +13462,7 @@
       </c>
       <c r="I77" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-SS-04 List files; TD-SS-10 Parameters and jobs as delivered</t>
+          <t>Data: TD-SS-04 List files; TD-SS-10 Parameters and jobs at their defaults</t>
         </is>
       </c>
       <c r="J77" s="12" t="inlineStr">
@@ -13992,16 +13481,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M77" s="12" t="inlineStr"/>
-      <c r="N77" s="27" t="inlineStr">
+      <c r="M77" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N77" s="12" t="n"/>
       <c r="O77" s="12" t="n"/>
-      <c r="P77" s="12" t="n"/>
-      <c r="Q77" s="28" t="n"/>
-      <c r="R77" s="12" t="n"/>
+      <c r="P77" s="28" t="n"/>
+      <c r="Q77" s="12" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="12" t="inlineStr">
@@ -14046,7 +13534,7 @@
       </c>
       <c r="I78" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-SS-04 List files; TD-SS-10 Parameters and jobs as delivered</t>
+          <t>Data: TD-SS-04 List files; TD-SS-10 Parameters and jobs at their defaults</t>
         </is>
       </c>
       <c r="J78" s="12" t="inlineStr">
@@ -14065,16 +13553,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M78" s="12" t="inlineStr"/>
-      <c r="N78" s="27" t="inlineStr">
+      <c r="M78" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N78" s="12" t="n"/>
       <c r="O78" s="12" t="n"/>
-      <c r="P78" s="12" t="n"/>
-      <c r="Q78" s="28" t="n"/>
-      <c r="R78" s="12" t="n"/>
+      <c r="P78" s="28" t="n"/>
+      <c r="Q78" s="12" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="12" t="inlineStr">
@@ -14120,7 +13607,7 @@
       <c r="I79" s="12" t="inlineStr">
         <is>
           <t>No failed record since the last digest.
-Data: TD-SS-04 List files; TD-SS-10 Parameters and jobs as delivered</t>
+Data: TD-SS-04 List files; TD-SS-10 Parameters and jobs at their defaults</t>
         </is>
       </c>
       <c r="J79" s="12" t="inlineStr">
@@ -14138,16 +13625,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M79" s="12" t="inlineStr"/>
-      <c r="N79" s="27" t="inlineStr">
+      <c r="M79" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N79" s="12" t="n"/>
       <c r="O79" s="12" t="n"/>
-      <c r="P79" s="12" t="n"/>
-      <c r="Q79" s="28" t="n"/>
-      <c r="R79" s="12" t="n"/>
+      <c r="P79" s="28" t="n"/>
+      <c r="Q79" s="12" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="12" t="inlineStr">
@@ -14193,7 +13679,7 @@
       <c r="I80" s="12" t="inlineStr">
         <is>
           <t>SCR_INGEST_ALERT_RECIPIENTS is empty; a run with failed records exists.
-Data: TD-SS-04 List files; TD-SS-10 Parameters and jobs as delivered</t>
+Data: TD-SS-04 List files; TD-SS-10 Parameters and jobs at their defaults</t>
         </is>
       </c>
       <c r="J80" s="12" t="inlineStr">
@@ -14211,16 +13697,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M80" s="12" t="inlineStr"/>
-      <c r="N80" s="27" t="inlineStr">
+      <c r="M80" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N80" s="12" t="n"/>
       <c r="O80" s="12" t="n"/>
-      <c r="P80" s="12" t="n"/>
-      <c r="Q80" s="28" t="n"/>
-      <c r="R80" s="12" t="n"/>
+      <c r="P80" s="28" t="n"/>
+      <c r="Q80" s="12" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="12" t="inlineStr">
@@ -14265,7 +13750,7 @@
       </c>
       <c r="I81" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-SS-04 List files; TD-SS-10 Parameters and jobs as delivered</t>
+          <t>Data: TD-SS-04 List files; TD-SS-10 Parameters and jobs at their defaults</t>
         </is>
       </c>
       <c r="J81" s="12" t="inlineStr">
@@ -14284,16 +13769,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M81" s="12" t="inlineStr"/>
-      <c r="N81" s="27" t="inlineStr">
+      <c r="M81" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N81" s="12" t="n"/>
       <c r="O81" s="12" t="n"/>
-      <c r="P81" s="12" t="n"/>
-      <c r="Q81" s="28" t="n"/>
-      <c r="R81" s="12" t="n"/>
+      <c r="P81" s="28" t="n"/>
+      <c r="Q81" s="12" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="12" t="inlineStr">
@@ -14357,16 +13841,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M82" s="12" t="inlineStr"/>
-      <c r="N82" s="27" t="inlineStr">
+      <c r="M82" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N82" s="12" t="n"/>
       <c r="O82" s="12" t="n"/>
-      <c r="P82" s="12" t="n"/>
-      <c r="Q82" s="28" t="n"/>
-      <c r="R82" s="12" t="n"/>
+      <c r="P82" s="28" t="n"/>
+      <c r="Q82" s="12" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="12" t="inlineStr">
@@ -14430,16 +13913,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M83" s="12" t="inlineStr"/>
-      <c r="N83" s="27" t="inlineStr">
+      <c r="M83" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N83" s="12" t="n"/>
       <c r="O83" s="12" t="n"/>
-      <c r="P83" s="12" t="n"/>
-      <c r="Q83" s="28" t="n"/>
-      <c r="R83" s="12" t="n"/>
+      <c r="P83" s="28" t="n"/>
+      <c r="Q83" s="12" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="12" t="inlineStr">
@@ -14503,16 +13985,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M84" s="12" t="inlineStr"/>
-      <c r="N84" s="27" t="inlineStr">
+      <c r="M84" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N84" s="12" t="n"/>
       <c r="O84" s="12" t="n"/>
-      <c r="P84" s="12" t="n"/>
-      <c r="Q84" s="28" t="n"/>
-      <c r="R84" s="12" t="n"/>
+      <c r="P84" s="28" t="n"/>
+      <c r="Q84" s="12" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="12" t="inlineStr">
@@ -14576,16 +14057,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M85" s="12" t="inlineStr"/>
-      <c r="N85" s="27" t="inlineStr">
+      <c r="M85" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N85" s="12" t="n"/>
       <c r="O85" s="12" t="n"/>
-      <c r="P85" s="12" t="n"/>
-      <c r="Q85" s="28" t="n"/>
-      <c r="R85" s="12" t="n"/>
+      <c r="P85" s="28" t="n"/>
+      <c r="Q85" s="12" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="12" t="inlineStr">
@@ -14649,16 +14129,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M86" s="12" t="inlineStr"/>
-      <c r="N86" s="27" t="inlineStr">
+      <c r="M86" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N86" s="12" t="n"/>
       <c r="O86" s="12" t="n"/>
-      <c r="P86" s="12" t="n"/>
-      <c r="Q86" s="28" t="n"/>
-      <c r="R86" s="12" t="n"/>
+      <c r="P86" s="28" t="n"/>
+      <c r="Q86" s="12" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="12" t="inlineStr">
@@ -14721,16 +14200,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M87" s="12" t="inlineStr"/>
-      <c r="N87" s="27" t="inlineStr">
+      <c r="M87" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N87" s="12" t="n"/>
       <c r="O87" s="12" t="n"/>
-      <c r="P87" s="12" t="n"/>
-      <c r="Q87" s="28" t="n"/>
-      <c r="R87" s="12" t="n"/>
+      <c r="P87" s="28" t="n"/>
+      <c r="Q87" s="12" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="12" t="inlineStr">
@@ -14795,16 +14273,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M88" s="12" t="inlineStr"/>
-      <c r="N88" s="27" t="inlineStr">
+      <c r="M88" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N88" s="12" t="n"/>
       <c r="O88" s="12" t="n"/>
-      <c r="P88" s="12" t="n"/>
-      <c r="Q88" s="28" t="n"/>
-      <c r="R88" s="12" t="n"/>
+      <c r="P88" s="28" t="n"/>
+      <c r="Q88" s="12" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="12" t="inlineStr">
@@ -14867,16 +14344,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M89" s="12" t="inlineStr"/>
-      <c r="N89" s="27" t="inlineStr">
+      <c r="M89" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N89" s="12" t="n"/>
       <c r="O89" s="12" t="n"/>
-      <c r="P89" s="12" t="n"/>
-      <c r="Q89" s="28" t="n"/>
-      <c r="R89" s="12" t="n"/>
+      <c r="P89" s="28" t="n"/>
+      <c r="Q89" s="12" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="12" t="inlineStr">
@@ -14940,16 +14416,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M90" s="12" t="inlineStr"/>
-      <c r="N90" s="27" t="inlineStr">
+      <c r="M90" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N90" s="12" t="n"/>
       <c r="O90" s="12" t="n"/>
-      <c r="P90" s="12" t="n"/>
-      <c r="Q90" s="28" t="n"/>
-      <c r="R90" s="12" t="n"/>
+      <c r="P90" s="28" t="n"/>
+      <c r="Q90" s="12" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="12" t="inlineStr">
@@ -15014,16 +14489,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M91" s="12" t="inlineStr"/>
-      <c r="N91" s="27" t="inlineStr">
+      <c r="M91" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N91" s="12" t="n"/>
       <c r="O91" s="12" t="n"/>
-      <c r="P91" s="12" t="n"/>
-      <c r="Q91" s="28" t="n"/>
-      <c r="R91" s="12" t="n"/>
+      <c r="P91" s="28" t="n"/>
+      <c r="Q91" s="12" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="12" t="inlineStr">
@@ -15086,16 +14560,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M92" s="12" t="inlineStr"/>
-      <c r="N92" s="27" t="inlineStr">
+      <c r="M92" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N92" s="12" t="n"/>
       <c r="O92" s="12" t="n"/>
-      <c r="P92" s="12" t="n"/>
-      <c r="Q92" s="28" t="n"/>
-      <c r="R92" s="12" t="n"/>
+      <c r="P92" s="28" t="n"/>
+      <c r="Q92" s="12" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="12" t="inlineStr">
@@ -15140,7 +14613,7 @@
       </c>
       <c r="I93" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-SS-05 Masked clients; TD-SS-10 Parameters and jobs as delivered</t>
+          <t>Data: TD-SS-05 Masked clients; TD-SS-10 Parameters and jobs at their defaults</t>
         </is>
       </c>
       <c r="J93" s="12" t="inlineStr">
@@ -15159,16 +14632,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M93" s="12" t="inlineStr"/>
-      <c r="N93" s="27" t="inlineStr">
+      <c r="M93" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N93" s="12" t="n"/>
       <c r="O93" s="12" t="n"/>
-      <c r="P93" s="12" t="n"/>
-      <c r="Q93" s="28" t="n"/>
-      <c r="R93" s="12" t="n"/>
+      <c r="P93" s="28" t="n"/>
+      <c r="Q93" s="12" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="12" t="inlineStr">
@@ -15213,7 +14685,7 @@
       </c>
       <c r="I94" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-SS-05 Masked clients; TD-SS-10 Parameters and jobs as delivered</t>
+          <t>Data: TD-SS-05 Masked clients; TD-SS-10 Parameters and jobs at their defaults</t>
         </is>
       </c>
       <c r="J94" s="12" t="inlineStr">
@@ -15231,16 +14703,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M94" s="12" t="inlineStr"/>
-      <c r="N94" s="27" t="inlineStr">
+      <c r="M94" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N94" s="12" t="n"/>
       <c r="O94" s="12" t="n"/>
-      <c r="P94" s="12" t="n"/>
-      <c r="Q94" s="28" t="n"/>
-      <c r="R94" s="12" t="n"/>
+      <c r="P94" s="28" t="n"/>
+      <c r="Q94" s="12" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="12" t="inlineStr">
@@ -15285,7 +14756,7 @@
       </c>
       <c r="I95" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-SS-05 Masked clients; TD-SS-10 Parameters and jobs as delivered</t>
+          <t>Data: TD-SS-05 Masked clients; TD-SS-10 Parameters and jobs at their defaults</t>
         </is>
       </c>
       <c r="J95" s="12" t="inlineStr">
@@ -15303,16 +14774,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M95" s="12" t="inlineStr"/>
-      <c r="N95" s="27" t="inlineStr">
+      <c r="M95" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N95" s="12" t="n"/>
       <c r="O95" s="12" t="n"/>
-      <c r="P95" s="12" t="n"/>
-      <c r="Q95" s="28" t="n"/>
-      <c r="R95" s="12" t="n"/>
+      <c r="P95" s="28" t="n"/>
+      <c r="Q95" s="12" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="12" t="inlineStr">
@@ -15357,7 +14827,7 @@
       </c>
       <c r="I96" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-SS-05 Masked clients; TD-SS-10 Parameters and jobs as delivered</t>
+          <t>Data: TD-SS-05 Masked clients; TD-SS-10 Parameters and jobs at their defaults</t>
         </is>
       </c>
       <c r="J96" s="12" t="inlineStr">
@@ -15375,16 +14845,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M96" s="12" t="inlineStr"/>
-      <c r="N96" s="27" t="inlineStr">
+      <c r="M96" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N96" s="12" t="n"/>
       <c r="O96" s="12" t="n"/>
-      <c r="P96" s="12" t="n"/>
-      <c r="Q96" s="28" t="n"/>
-      <c r="R96" s="12" t="n"/>
+      <c r="P96" s="28" t="n"/>
+      <c r="Q96" s="12" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="12" t="inlineStr">
@@ -15429,7 +14898,7 @@
       </c>
       <c r="I97" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-SS-05 Masked clients; TD-SS-10 Parameters and jobs as delivered</t>
+          <t>Data: TD-SS-05 Masked clients; TD-SS-10 Parameters and jobs at their defaults</t>
         </is>
       </c>
       <c r="J97" s="12" t="inlineStr">
@@ -15447,16 +14916,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M97" s="12" t="inlineStr"/>
-      <c r="N97" s="27" t="inlineStr">
+      <c r="M97" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N97" s="12" t="n"/>
       <c r="O97" s="12" t="n"/>
-      <c r="P97" s="12" t="n"/>
-      <c r="Q97" s="28" t="n"/>
-      <c r="R97" s="12" t="n"/>
+      <c r="P97" s="28" t="n"/>
+      <c r="Q97" s="12" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="12" t="inlineStr">
@@ -15501,7 +14969,7 @@
       </c>
       <c r="I98" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-SS-05 Masked clients; TD-SS-10 Parameters and jobs as delivered</t>
+          <t>Data: TD-SS-05 Masked clients; TD-SS-10 Parameters and jobs at their defaults</t>
         </is>
       </c>
       <c r="J98" s="12" t="inlineStr">
@@ -15519,16 +14987,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M98" s="12" t="inlineStr"/>
-      <c r="N98" s="27" t="inlineStr">
+      <c r="M98" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N98" s="12" t="n"/>
       <c r="O98" s="12" t="n"/>
-      <c r="P98" s="12" t="n"/>
-      <c r="Q98" s="28" t="n"/>
-      <c r="R98" s="12" t="n"/>
+      <c r="P98" s="28" t="n"/>
+      <c r="Q98" s="12" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="12" t="inlineStr">
@@ -15573,7 +15040,7 @@
       </c>
       <c r="I99" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-SS-05 Masked clients; TD-SS-10 Parameters and jobs as delivered</t>
+          <t>Data: TD-SS-05 Masked clients; TD-SS-10 Parameters and jobs at their defaults</t>
         </is>
       </c>
       <c r="J99" s="12" t="inlineStr">
@@ -15591,16 +15058,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M99" s="12" t="inlineStr"/>
-      <c r="N99" s="27" t="inlineStr">
+      <c r="M99" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N99" s="12" t="n"/>
       <c r="O99" s="12" t="n"/>
-      <c r="P99" s="12" t="n"/>
-      <c r="Q99" s="28" t="n"/>
-      <c r="R99" s="12" t="n"/>
+      <c r="P99" s="28" t="n"/>
+      <c r="Q99" s="12" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="12" t="inlineStr">
@@ -15664,16 +15130,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M100" s="12" t="inlineStr"/>
-      <c r="N100" s="27" t="inlineStr">
+      <c r="M100" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N100" s="12" t="n"/>
       <c r="O100" s="12" t="n"/>
-      <c r="P100" s="12" t="n"/>
-      <c r="Q100" s="28" t="n"/>
-      <c r="R100" s="12" t="n"/>
+      <c r="P100" s="28" t="n"/>
+      <c r="Q100" s="12" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="12" t="inlineStr">
@@ -15736,16 +15201,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M101" s="12" t="inlineStr"/>
-      <c r="N101" s="27" t="inlineStr">
+      <c r="M101" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N101" s="12" t="n"/>
       <c r="O101" s="12" t="n"/>
-      <c r="P101" s="12" t="n"/>
-      <c r="Q101" s="28" t="n"/>
-      <c r="R101" s="12" t="n"/>
+      <c r="P101" s="28" t="n"/>
+      <c r="Q101" s="12" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="12" t="inlineStr">
@@ -15808,16 +15272,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M102" s="12" t="inlineStr"/>
-      <c r="N102" s="27" t="inlineStr">
+      <c r="M102" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N102" s="12" t="n"/>
       <c r="O102" s="12" t="n"/>
-      <c r="P102" s="12" t="n"/>
-      <c r="Q102" s="28" t="n"/>
-      <c r="R102" s="12" t="n"/>
+      <c r="P102" s="28" t="n"/>
+      <c r="Q102" s="12" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="12" t="inlineStr">
@@ -15881,16 +15344,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M103" s="12" t="inlineStr"/>
-      <c r="N103" s="27" t="inlineStr">
+      <c r="M103" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N103" s="12" t="n"/>
       <c r="O103" s="12" t="n"/>
-      <c r="P103" s="12" t="n"/>
-      <c r="Q103" s="28" t="n"/>
-      <c r="R103" s="12" t="n"/>
+      <c r="P103" s="28" t="n"/>
+      <c r="Q103" s="12" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="12" t="inlineStr">
@@ -15953,16 +15415,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M104" s="12" t="inlineStr"/>
-      <c r="N104" s="27" t="inlineStr">
+      <c r="M104" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N104" s="12" t="n"/>
       <c r="O104" s="12" t="n"/>
-      <c r="P104" s="12" t="n"/>
-      <c r="Q104" s="28" t="n"/>
-      <c r="R104" s="12" t="n"/>
+      <c r="P104" s="28" t="n"/>
+      <c r="Q104" s="12" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="12" t="inlineStr">
@@ -16026,16 +15487,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M105" s="12" t="inlineStr"/>
-      <c r="N105" s="27" t="inlineStr">
+      <c r="M105" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N105" s="12" t="n"/>
       <c r="O105" s="12" t="n"/>
-      <c r="P105" s="12" t="n"/>
-      <c r="Q105" s="28" t="n"/>
-      <c r="R105" s="12" t="n"/>
+      <c r="P105" s="28" t="n"/>
+      <c r="Q105" s="12" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="12" t="inlineStr">
@@ -16099,16 +15559,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M106" s="12" t="inlineStr"/>
-      <c r="N106" s="27" t="inlineStr">
+      <c r="M106" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N106" s="12" t="n"/>
       <c r="O106" s="12" t="n"/>
-      <c r="P106" s="12" t="n"/>
-      <c r="Q106" s="28" t="n"/>
-      <c r="R106" s="12" t="n"/>
+      <c r="P106" s="28" t="n"/>
+      <c r="Q106" s="12" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="12" t="inlineStr">
@@ -16172,16 +15631,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M107" s="12" t="inlineStr"/>
-      <c r="N107" s="27" t="inlineStr">
+      <c r="M107" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N107" s="12" t="n"/>
       <c r="O107" s="12" t="n"/>
-      <c r="P107" s="12" t="n"/>
-      <c r="Q107" s="28" t="n"/>
-      <c r="R107" s="12" t="n"/>
+      <c r="P107" s="28" t="n"/>
+      <c r="Q107" s="12" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="12" t="inlineStr">
@@ -16245,16 +15703,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M108" s="12" t="inlineStr"/>
-      <c r="N108" s="27" t="inlineStr">
+      <c r="M108" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N108" s="12" t="n"/>
       <c r="O108" s="12" t="n"/>
-      <c r="P108" s="12" t="n"/>
-      <c r="Q108" s="28" t="n"/>
-      <c r="R108" s="12" t="n"/>
+      <c r="P108" s="28" t="n"/>
+      <c r="Q108" s="12" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="12" t="inlineStr">
@@ -16317,16 +15774,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M109" s="12" t="inlineStr"/>
-      <c r="N109" s="27" t="inlineStr">
+      <c r="M109" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N109" s="12" t="n"/>
       <c r="O109" s="12" t="n"/>
-      <c r="P109" s="12" t="n"/>
-      <c r="Q109" s="28" t="n"/>
-      <c r="R109" s="12" t="n"/>
+      <c r="P109" s="28" t="n"/>
+      <c r="Q109" s="12" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="12" t="inlineStr">
@@ -16389,16 +15845,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M110" s="12" t="inlineStr"/>
-      <c r="N110" s="27" t="inlineStr">
+      <c r="M110" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N110" s="12" t="n"/>
       <c r="O110" s="12" t="n"/>
-      <c r="P110" s="12" t="n"/>
-      <c r="Q110" s="28" t="n"/>
-      <c r="R110" s="12" t="n"/>
+      <c r="P110" s="28" t="n"/>
+      <c r="Q110" s="12" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="12" t="inlineStr">
@@ -16461,16 +15916,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M111" s="12" t="inlineStr"/>
-      <c r="N111" s="27" t="inlineStr">
+      <c r="M111" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N111" s="12" t="n"/>
       <c r="O111" s="12" t="n"/>
-      <c r="P111" s="12" t="n"/>
-      <c r="Q111" s="28" t="n"/>
-      <c r="R111" s="12" t="n"/>
+      <c r="P111" s="28" t="n"/>
+      <c r="Q111" s="12" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="12" t="inlineStr">
@@ -16534,16 +15988,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M112" s="12" t="inlineStr"/>
-      <c r="N112" s="27" t="inlineStr">
+      <c r="M112" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N112" s="12" t="n"/>
       <c r="O112" s="12" t="n"/>
-      <c r="P112" s="12" t="n"/>
-      <c r="Q112" s="28" t="n"/>
-      <c r="R112" s="12" t="n"/>
+      <c r="P112" s="28" t="n"/>
+      <c r="Q112" s="12" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="12" t="inlineStr">
@@ -16606,16 +16059,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M113" s="12" t="inlineStr"/>
-      <c r="N113" s="27" t="inlineStr">
+      <c r="M113" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N113" s="12" t="n"/>
       <c r="O113" s="12" t="n"/>
-      <c r="P113" s="12" t="n"/>
-      <c r="Q113" s="28" t="n"/>
-      <c r="R113" s="12" t="n"/>
+      <c r="P113" s="28" t="n"/>
+      <c r="Q113" s="12" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="12" t="inlineStr">
@@ -16679,16 +16131,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M114" s="12" t="inlineStr"/>
-      <c r="N114" s="27" t="inlineStr">
+      <c r="M114" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N114" s="12" t="n"/>
       <c r="O114" s="12" t="n"/>
-      <c r="P114" s="12" t="n"/>
-      <c r="Q114" s="28" t="n"/>
-      <c r="R114" s="12" t="n"/>
+      <c r="P114" s="28" t="n"/>
+      <c r="Q114" s="12" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="12" t="inlineStr">
@@ -16751,16 +16202,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M115" s="12" t="inlineStr"/>
-      <c r="N115" s="27" t="inlineStr">
+      <c r="M115" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N115" s="12" t="n"/>
       <c r="O115" s="12" t="n"/>
-      <c r="P115" s="12" t="n"/>
-      <c r="Q115" s="28" t="n"/>
-      <c r="R115" s="12" t="n"/>
+      <c r="P115" s="28" t="n"/>
+      <c r="Q115" s="12" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="12" t="inlineStr">
@@ -16823,16 +16273,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M116" s="12" t="inlineStr"/>
-      <c r="N116" s="27" t="inlineStr">
+      <c r="M116" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N116" s="12" t="n"/>
       <c r="O116" s="12" t="n"/>
-      <c r="P116" s="12" t="n"/>
-      <c r="Q116" s="28" t="n"/>
-      <c r="R116" s="12" t="n"/>
+      <c r="P116" s="28" t="n"/>
+      <c r="Q116" s="12" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="12" t="inlineStr">
@@ -16896,16 +16345,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M117" s="12" t="inlineStr"/>
-      <c r="N117" s="27" t="inlineStr">
+      <c r="M117" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N117" s="12" t="n"/>
       <c r="O117" s="12" t="n"/>
-      <c r="P117" s="12" t="n"/>
-      <c r="Q117" s="28" t="n"/>
-      <c r="R117" s="12" t="n"/>
+      <c r="P117" s="28" t="n"/>
+      <c r="Q117" s="12" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="12" t="inlineStr">
@@ -16969,16 +16417,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M118" s="12" t="inlineStr"/>
-      <c r="N118" s="27" t="inlineStr">
+      <c r="M118" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N118" s="12" t="n"/>
       <c r="O118" s="12" t="n"/>
-      <c r="P118" s="12" t="n"/>
-      <c r="Q118" s="28" t="n"/>
-      <c r="R118" s="12" t="n"/>
+      <c r="P118" s="28" t="n"/>
+      <c r="Q118" s="12" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="12" t="inlineStr">
@@ -17042,16 +16489,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M119" s="12" t="inlineStr"/>
-      <c r="N119" s="27" t="inlineStr">
+      <c r="M119" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N119" s="12" t="n"/>
       <c r="O119" s="12" t="n"/>
-      <c r="P119" s="12" t="n"/>
-      <c r="Q119" s="28" t="n"/>
-      <c r="R119" s="12" t="n"/>
+      <c r="P119" s="28" t="n"/>
+      <c r="Q119" s="12" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="12" t="inlineStr">
@@ -17115,16 +16561,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M120" s="12" t="inlineStr"/>
-      <c r="N120" s="27" t="inlineStr">
+      <c r="M120" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N120" s="12" t="n"/>
       <c r="O120" s="12" t="n"/>
-      <c r="P120" s="12" t="n"/>
-      <c r="Q120" s="28" t="n"/>
-      <c r="R120" s="12" t="n"/>
+      <c r="P120" s="28" t="n"/>
+      <c r="Q120" s="12" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="12" t="inlineStr">
@@ -17164,7 +16609,7 @@
       </c>
       <c r="H121" s="12" t="inlineStr">
         <is>
-          <t>API call with the user's token (tester tool, for example Postman)</t>
+          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I121" s="12" t="inlineStr">
@@ -17188,16 +16633,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M121" s="12" t="inlineStr"/>
-      <c r="N121" s="27" t="inlineStr">
+      <c r="M121" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N121" s="12" t="n"/>
       <c r="O121" s="12" t="n"/>
-      <c r="P121" s="12" t="n"/>
-      <c r="Q121" s="28" t="n"/>
-      <c r="R121" s="12" t="n"/>
+      <c r="P121" s="28" t="n"/>
+      <c r="Q121" s="12" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="12" t="inlineStr">
@@ -17260,16 +16704,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M122" s="12" t="inlineStr"/>
-      <c r="N122" s="27" t="inlineStr">
+      <c r="M122" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N122" s="12" t="n"/>
       <c r="O122" s="12" t="n"/>
-      <c r="P122" s="12" t="n"/>
-      <c r="Q122" s="28" t="n"/>
-      <c r="R122" s="12" t="n"/>
+      <c r="P122" s="28" t="n"/>
+      <c r="Q122" s="12" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="12" t="inlineStr">
@@ -17319,12 +16762,12 @@
       </c>
       <c r="J123" s="12" t="inlineStr">
         <is>
-          <t>1. Submit a case; reopen it; try Save Draft on the Review tab through the API.</t>
+          <t>1. Submit a case; reopen it; try Save Draft on the Review tab by a direct request.</t>
         </is>
       </c>
       <c r="K123" s="12" t="inlineStr">
         <is>
-          <t>The case is read only; the call is refused.
+          <t>The case is read only; a direct request is refused.
 Message "Case SCR-2026-000012 is no longer assigned to you".</t>
         </is>
       </c>
@@ -17333,16 +16776,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M123" s="12" t="inlineStr"/>
-      <c r="N123" s="27" t="inlineStr">
+      <c r="M123" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N123" s="12" t="n"/>
       <c r="O123" s="12" t="n"/>
-      <c r="P123" s="12" t="n"/>
-      <c r="Q123" s="28" t="n"/>
-      <c r="R123" s="12" t="n"/>
+      <c r="P123" s="28" t="n"/>
+      <c r="Q123" s="12" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="12" t="inlineStr">
@@ -17405,16 +16847,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M124" s="12" t="inlineStr"/>
-      <c r="N124" s="27" t="inlineStr">
+      <c r="M124" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N124" s="12" t="n"/>
       <c r="O124" s="12" t="n"/>
-      <c r="P124" s="12" t="n"/>
-      <c r="Q124" s="28" t="n"/>
-      <c r="R124" s="12" t="n"/>
+      <c r="P124" s="28" t="n"/>
+      <c r="Q124" s="12" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="12" t="inlineStr">
@@ -17454,7 +16895,7 @@
       </c>
       <c r="H125" s="12" t="inlineStr">
         <is>
-          <t>API call with the user's token (tester tool, for example Postman)</t>
+          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I125" s="12" t="inlineStr">
@@ -17464,13 +16905,13 @@
       </c>
       <c r="J125" s="12" t="inlineStr">
         <is>
-          <t>1. Call prepare_str on a case in UNIT_HEAD_APPROVAL.</t>
+          <t>1. Send a direct request for the action Prepare STR on a case in UNIT_HEAD_APPROVAL.</t>
         </is>
       </c>
       <c r="K125" s="12" t="inlineStr">
         <is>
           <t>Refused; the case stays.
-Message "The action prepare_str is not allowed in stage UNIT_HEAD_APPROVAL".</t>
+Message "The action Prepare STR is not allowed in stage UNIT_HEAD_APPROVAL".</t>
         </is>
       </c>
       <c r="L125" s="12" t="inlineStr">
@@ -17478,16 +16919,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M125" s="12" t="inlineStr"/>
-      <c r="N125" s="27" t="inlineStr">
+      <c r="M125" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N125" s="12" t="n"/>
       <c r="O125" s="12" t="n"/>
-      <c r="P125" s="12" t="n"/>
-      <c r="Q125" s="28" t="n"/>
-      <c r="R125" s="12" t="n"/>
+      <c r="P125" s="28" t="n"/>
+      <c r="Q125" s="12" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="12" t="inlineStr">
@@ -17550,16 +16990,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M126" s="12" t="inlineStr"/>
-      <c r="N126" s="27" t="inlineStr">
+      <c r="M126" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N126" s="12" t="n"/>
       <c r="O126" s="12" t="n"/>
-      <c r="P126" s="12" t="n"/>
-      <c r="Q126" s="28" t="n"/>
-      <c r="R126" s="12" t="n"/>
+      <c r="P126" s="28" t="n"/>
+      <c r="Q126" s="12" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="12" t="inlineStr">
@@ -17622,16 +17061,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M127" s="12" t="inlineStr"/>
-      <c r="N127" s="27" t="inlineStr">
+      <c r="M127" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N127" s="12" t="n"/>
       <c r="O127" s="12" t="n"/>
-      <c r="P127" s="12" t="n"/>
-      <c r="Q127" s="28" t="n"/>
-      <c r="R127" s="12" t="n"/>
+      <c r="P127" s="28" t="n"/>
+      <c r="Q127" s="12" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="12" t="inlineStr">
@@ -17694,16 +17132,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M128" s="12" t="inlineStr"/>
-      <c r="N128" s="27" t="inlineStr">
+      <c r="M128" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N128" s="12" t="n"/>
       <c r="O128" s="12" t="n"/>
-      <c r="P128" s="12" t="n"/>
-      <c r="Q128" s="28" t="n"/>
-      <c r="R128" s="12" t="n"/>
+      <c r="P128" s="28" t="n"/>
+      <c r="Q128" s="12" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="12" t="inlineStr">
@@ -17766,16 +17203,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M129" s="12" t="inlineStr"/>
-      <c r="N129" s="27" t="inlineStr">
+      <c r="M129" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N129" s="12" t="n"/>
       <c r="O129" s="12" t="n"/>
-      <c r="P129" s="12" t="n"/>
-      <c r="Q129" s="28" t="n"/>
-      <c r="R129" s="12" t="n"/>
+      <c r="P129" s="28" t="n"/>
+      <c r="Q129" s="12" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="12" t="inlineStr">
@@ -17838,16 +17274,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M130" s="12" t="inlineStr"/>
-      <c r="N130" s="27" t="inlineStr">
+      <c r="M130" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N130" s="12" t="n"/>
       <c r="O130" s="12" t="n"/>
-      <c r="P130" s="12" t="n"/>
-      <c r="Q130" s="28" t="n"/>
-      <c r="R130" s="12" t="n"/>
+      <c r="P130" s="28" t="n"/>
+      <c r="Q130" s="12" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="12" t="inlineStr">
@@ -17911,16 +17346,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M131" s="12" t="inlineStr"/>
-      <c r="N131" s="27" t="inlineStr">
+      <c r="M131" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N131" s="12" t="n"/>
       <c r="O131" s="12" t="n"/>
-      <c r="P131" s="12" t="n"/>
-      <c r="Q131" s="28" t="n"/>
-      <c r="R131" s="12" t="n"/>
+      <c r="P131" s="28" t="n"/>
+      <c r="Q131" s="12" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="12" t="inlineStr">
@@ -17983,16 +17417,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M132" s="12" t="inlineStr"/>
-      <c r="N132" s="27" t="inlineStr">
+      <c r="M132" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N132" s="12" t="n"/>
       <c r="O132" s="12" t="n"/>
-      <c r="P132" s="12" t="n"/>
-      <c r="Q132" s="28" t="n"/>
-      <c r="R132" s="12" t="n"/>
+      <c r="P132" s="28" t="n"/>
+      <c r="Q132" s="12" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="12" t="inlineStr">
@@ -18055,16 +17488,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M133" s="12" t="inlineStr"/>
-      <c r="N133" s="27" t="inlineStr">
+      <c r="M133" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N133" s="12" t="n"/>
       <c r="O133" s="12" t="n"/>
-      <c r="P133" s="12" t="n"/>
-      <c r="Q133" s="28" t="n"/>
-      <c r="R133" s="12" t="n"/>
+      <c r="P133" s="28" t="n"/>
+      <c r="Q133" s="12" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="12" t="inlineStr">
@@ -18128,16 +17560,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M134" s="12" t="inlineStr"/>
-      <c r="N134" s="27" t="inlineStr">
+      <c r="M134" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N134" s="12" t="n"/>
       <c r="O134" s="12" t="n"/>
-      <c r="P134" s="12" t="n"/>
-      <c r="Q134" s="28" t="n"/>
-      <c r="R134" s="12" t="n"/>
+      <c r="P134" s="28" t="n"/>
+      <c r="Q134" s="12" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="12" t="inlineStr">
@@ -18200,16 +17631,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M135" s="12" t="inlineStr"/>
-      <c r="N135" s="27" t="inlineStr">
+      <c r="M135" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N135" s="12" t="n"/>
       <c r="O135" s="12" t="n"/>
-      <c r="P135" s="12" t="n"/>
-      <c r="Q135" s="28" t="n"/>
-      <c r="R135" s="12" t="n"/>
+      <c r="P135" s="28" t="n"/>
+      <c r="Q135" s="12" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="12" t="inlineStr">
@@ -18273,16 +17703,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M136" s="12" t="inlineStr"/>
-      <c r="N136" s="27" t="inlineStr">
+      <c r="M136" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N136" s="12" t="n"/>
       <c r="O136" s="12" t="n"/>
-      <c r="P136" s="12" t="n"/>
-      <c r="Q136" s="28" t="n"/>
-      <c r="R136" s="12" t="n"/>
+      <c r="P136" s="28" t="n"/>
+      <c r="Q136" s="12" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="12" t="inlineStr">
@@ -18322,7 +17751,7 @@
       </c>
       <c r="H137" s="12" t="inlineStr">
         <is>
-          <t>API call with the user's token (tester tool, for example Postman)</t>
+          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I137" s="12" t="inlineStr">
@@ -18346,16 +17775,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M137" s="12" t="inlineStr"/>
-      <c r="N137" s="27" t="inlineStr">
+      <c r="M137" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N137" s="12" t="n"/>
       <c r="O137" s="12" t="n"/>
-      <c r="P137" s="12" t="n"/>
-      <c r="Q137" s="28" t="n"/>
-      <c r="R137" s="12" t="n"/>
+      <c r="P137" s="28" t="n"/>
+      <c r="Q137" s="12" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="12" t="inlineStr">
@@ -18418,16 +17846,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M138" s="12" t="inlineStr"/>
-      <c r="N138" s="27" t="inlineStr">
+      <c r="M138" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N138" s="12" t="n"/>
       <c r="O138" s="12" t="n"/>
-      <c r="P138" s="12" t="n"/>
-      <c r="Q138" s="28" t="n"/>
-      <c r="R138" s="12" t="n"/>
+      <c r="P138" s="28" t="n"/>
+      <c r="Q138" s="12" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="12" t="inlineStr">
@@ -18491,16 +17918,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M139" s="12" t="inlineStr"/>
-      <c r="N139" s="27" t="inlineStr">
+      <c r="M139" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N139" s="12" t="n"/>
       <c r="O139" s="12" t="n"/>
-      <c r="P139" s="12" t="n"/>
-      <c r="Q139" s="28" t="n"/>
-      <c r="R139" s="12" t="n"/>
+      <c r="P139" s="28" t="n"/>
+      <c r="Q139" s="12" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="12" t="inlineStr">
@@ -18564,16 +17990,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M140" s="12" t="inlineStr"/>
-      <c r="N140" s="27" t="inlineStr">
+      <c r="M140" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N140" s="12" t="n"/>
       <c r="O140" s="12" t="n"/>
-      <c r="P140" s="12" t="n"/>
-      <c r="Q140" s="28" t="n"/>
-      <c r="R140" s="12" t="n"/>
+      <c r="P140" s="28" t="n"/>
+      <c r="Q140" s="12" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="12" t="inlineStr">
@@ -18619,7 +18044,7 @@
       <c r="I141" s="12" t="inlineStr">
         <is>
           <t>A case due in 2 hours with a 4-hour lead.
-Data: TD-SS-06 Cases in every stage; TD-SS-10 Parameters and jobs as delivered</t>
+Data: TD-SS-06 Cases in every stage; TD-SS-10 Parameters and jobs at their defaults</t>
         </is>
       </c>
       <c r="J141" s="12" t="inlineStr">
@@ -18637,16 +18062,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M141" s="12" t="inlineStr"/>
-      <c r="N141" s="27" t="inlineStr">
+      <c r="M141" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N141" s="12" t="n"/>
       <c r="O141" s="12" t="n"/>
-      <c r="P141" s="12" t="n"/>
-      <c r="Q141" s="28" t="n"/>
-      <c r="R141" s="12" t="n"/>
+      <c r="P141" s="28" t="n"/>
+      <c r="Q141" s="12" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="12" t="inlineStr">
@@ -18692,7 +18116,7 @@
       <c r="I142" s="12" t="inlineStr">
         <is>
           <t>A case due in 5 hours with a 4-hour lead.
-Data: TD-SS-06 Cases in every stage; TD-SS-10 Parameters and jobs as delivered</t>
+Data: TD-SS-06 Cases in every stage; TD-SS-10 Parameters and jobs at their defaults</t>
         </is>
       </c>
       <c r="J142" s="12" t="inlineStr">
@@ -18710,16 +18134,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M142" s="12" t="inlineStr"/>
-      <c r="N142" s="27" t="inlineStr">
+      <c r="M142" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N142" s="12" t="n"/>
       <c r="O142" s="12" t="n"/>
-      <c r="P142" s="12" t="n"/>
-      <c r="Q142" s="28" t="n"/>
-      <c r="R142" s="12" t="n"/>
+      <c r="P142" s="28" t="n"/>
+      <c r="Q142" s="12" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="12" t="inlineStr">
@@ -18765,7 +18188,7 @@
       <c r="I143" s="12" t="inlineStr">
         <is>
           <t>A case past its due time.
-Data: TD-SS-06 Cases in every stage; TD-SS-10 Parameters and jobs as delivered</t>
+Data: TD-SS-06 Cases in every stage; TD-SS-10 Parameters and jobs at their defaults</t>
         </is>
       </c>
       <c r="J143" s="12" t="inlineStr">
@@ -18783,16 +18206,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M143" s="12" t="inlineStr"/>
-      <c r="N143" s="27" t="inlineStr">
+      <c r="M143" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N143" s="12" t="n"/>
       <c r="O143" s="12" t="n"/>
-      <c r="P143" s="12" t="n"/>
-      <c r="Q143" s="28" t="n"/>
-      <c r="R143" s="12" t="n"/>
+      <c r="P143" s="28" t="n"/>
+      <c r="Q143" s="12" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="12" t="inlineStr">
@@ -18837,7 +18259,7 @@
       </c>
       <c r="I144" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-SS-06 Cases in every stage; TD-SS-10 Parameters and jobs as delivered</t>
+          <t>Data: TD-SS-06 Cases in every stage; TD-SS-10 Parameters and jobs at their defaults</t>
         </is>
       </c>
       <c r="J144" s="12" t="inlineStr">
@@ -18855,16 +18277,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M144" s="12" t="inlineStr"/>
-      <c r="N144" s="27" t="inlineStr">
+      <c r="M144" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N144" s="12" t="n"/>
       <c r="O144" s="12" t="n"/>
-      <c r="P144" s="12" t="n"/>
-      <c r="Q144" s="28" t="n"/>
-      <c r="R144" s="12" t="n"/>
+      <c r="P144" s="28" t="n"/>
+      <c r="Q144" s="12" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="12" t="inlineStr">
@@ -18927,16 +18348,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M145" s="12" t="inlineStr"/>
-      <c r="N145" s="27" t="inlineStr">
+      <c r="M145" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N145" s="12" t="n"/>
       <c r="O145" s="12" t="n"/>
-      <c r="P145" s="12" t="n"/>
-      <c r="Q145" s="28" t="n"/>
-      <c r="R145" s="12" t="n"/>
+      <c r="P145" s="28" t="n"/>
+      <c r="Q145" s="12" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="12" t="inlineStr">
@@ -18999,16 +18419,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M146" s="12" t="inlineStr"/>
-      <c r="N146" s="27" t="inlineStr">
+      <c r="M146" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N146" s="12" t="n"/>
       <c r="O146" s="12" t="n"/>
-      <c r="P146" s="12" t="n"/>
-      <c r="Q146" s="28" t="n"/>
-      <c r="R146" s="12" t="n"/>
+      <c r="P146" s="28" t="n"/>
+      <c r="Q146" s="12" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="12" t="inlineStr">
@@ -19071,16 +18490,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M147" s="12" t="inlineStr"/>
-      <c r="N147" s="27" t="inlineStr">
+      <c r="M147" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N147" s="12" t="n"/>
       <c r="O147" s="12" t="n"/>
-      <c r="P147" s="12" t="n"/>
-      <c r="Q147" s="28" t="n"/>
-      <c r="R147" s="12" t="n"/>
+      <c r="P147" s="28" t="n"/>
+      <c r="Q147" s="12" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="12" t="inlineStr">
@@ -19143,16 +18561,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M148" s="12" t="inlineStr"/>
-      <c r="N148" s="27" t="inlineStr">
+      <c r="M148" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N148" s="12" t="n"/>
       <c r="O148" s="12" t="n"/>
-      <c r="P148" s="12" t="n"/>
-      <c r="Q148" s="28" t="n"/>
-      <c r="R148" s="12" t="n"/>
+      <c r="P148" s="28" t="n"/>
+      <c r="Q148" s="12" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="12" t="inlineStr">
@@ -19216,16 +18633,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M149" s="12" t="inlineStr"/>
-      <c r="N149" s="27" t="inlineStr">
+      <c r="M149" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N149" s="12" t="n"/>
       <c r="O149" s="12" t="n"/>
-      <c r="P149" s="12" t="n"/>
-      <c r="Q149" s="28" t="n"/>
-      <c r="R149" s="12" t="n"/>
+      <c r="P149" s="28" t="n"/>
+      <c r="Q149" s="12" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="12" t="inlineStr">
@@ -19289,16 +18705,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M150" s="12" t="inlineStr"/>
-      <c r="N150" s="27" t="inlineStr">
+      <c r="M150" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N150" s="12" t="n"/>
       <c r="O150" s="12" t="n"/>
-      <c r="P150" s="12" t="n"/>
-      <c r="Q150" s="28" t="n"/>
-      <c r="R150" s="12" t="n"/>
+      <c r="P150" s="28" t="n"/>
+      <c r="Q150" s="12" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="12" t="inlineStr">
@@ -19361,16 +18776,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M151" s="12" t="inlineStr"/>
-      <c r="N151" s="27" t="inlineStr">
+      <c r="M151" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N151" s="12" t="n"/>
       <c r="O151" s="12" t="n"/>
-      <c r="P151" s="12" t="n"/>
-      <c r="Q151" s="28" t="n"/>
-      <c r="R151" s="12" t="n"/>
+      <c r="P151" s="28" t="n"/>
+      <c r="Q151" s="12" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="12" t="inlineStr">
@@ -19433,16 +18847,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M152" s="12" t="inlineStr"/>
-      <c r="N152" s="27" t="inlineStr">
+      <c r="M152" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N152" s="12" t="n"/>
       <c r="O152" s="12" t="n"/>
-      <c r="P152" s="12" t="n"/>
-      <c r="Q152" s="28" t="n"/>
-      <c r="R152" s="12" t="n"/>
+      <c r="P152" s="28" t="n"/>
+      <c r="Q152" s="12" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="12" t="inlineStr">
@@ -19505,16 +18918,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M153" s="12" t="inlineStr"/>
-      <c r="N153" s="27" t="inlineStr">
+      <c r="M153" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N153" s="12" t="n"/>
       <c r="O153" s="12" t="n"/>
-      <c r="P153" s="12" t="n"/>
-      <c r="Q153" s="28" t="n"/>
-      <c r="R153" s="12" t="n"/>
+      <c r="P153" s="28" t="n"/>
+      <c r="Q153" s="12" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="12" t="inlineStr">
@@ -19578,16 +18990,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M154" s="12" t="inlineStr"/>
-      <c r="N154" s="27" t="inlineStr">
+      <c r="M154" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N154" s="12" t="n"/>
       <c r="O154" s="12" t="n"/>
-      <c r="P154" s="12" t="n"/>
-      <c r="Q154" s="28" t="n"/>
-      <c r="R154" s="12" t="n"/>
+      <c r="P154" s="28" t="n"/>
+      <c r="Q154" s="12" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="12" t="inlineStr">
@@ -19651,16 +19062,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M155" s="12" t="inlineStr"/>
-      <c r="N155" s="27" t="inlineStr">
+      <c r="M155" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N155" s="12" t="n"/>
       <c r="O155" s="12" t="n"/>
-      <c r="P155" s="12" t="n"/>
-      <c r="Q155" s="28" t="n"/>
-      <c r="R155" s="12" t="n"/>
+      <c r="P155" s="28" t="n"/>
+      <c r="Q155" s="12" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="12" t="inlineStr">
@@ -19723,16 +19133,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M156" s="12" t="inlineStr"/>
-      <c r="N156" s="27" t="inlineStr">
+      <c r="M156" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N156" s="12" t="n"/>
       <c r="O156" s="12" t="n"/>
-      <c r="P156" s="12" t="n"/>
-      <c r="Q156" s="28" t="n"/>
-      <c r="R156" s="12" t="n"/>
+      <c r="P156" s="28" t="n"/>
+      <c r="Q156" s="12" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="12" t="inlineStr">
@@ -19796,16 +19205,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M157" s="12" t="inlineStr"/>
-      <c r="N157" s="27" t="inlineStr">
+      <c r="M157" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N157" s="12" t="n"/>
       <c r="O157" s="12" t="n"/>
-      <c r="P157" s="12" t="n"/>
-      <c r="Q157" s="28" t="n"/>
-      <c r="R157" s="12" t="n"/>
+      <c r="P157" s="28" t="n"/>
+      <c r="Q157" s="12" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="12" t="inlineStr">
@@ -19869,16 +19277,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M158" s="12" t="inlineStr"/>
-      <c r="N158" s="27" t="inlineStr">
+      <c r="M158" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N158" s="12" t="n"/>
       <c r="O158" s="12" t="n"/>
-      <c r="P158" s="12" t="n"/>
-      <c r="Q158" s="28" t="n"/>
-      <c r="R158" s="12" t="n"/>
+      <c r="P158" s="28" t="n"/>
+      <c r="Q158" s="12" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="12" t="inlineStr">
@@ -19942,16 +19349,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M159" s="12" t="inlineStr"/>
-      <c r="N159" s="27" t="inlineStr">
+      <c r="M159" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N159" s="12" t="n"/>
       <c r="O159" s="12" t="n"/>
-      <c r="P159" s="12" t="n"/>
-      <c r="Q159" s="28" t="n"/>
-      <c r="R159" s="12" t="n"/>
+      <c r="P159" s="28" t="n"/>
+      <c r="Q159" s="12" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="12" t="inlineStr">
@@ -20015,16 +19421,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M160" s="12" t="inlineStr"/>
-      <c r="N160" s="27" t="inlineStr">
+      <c r="M160" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N160" s="12" t="n"/>
       <c r="O160" s="12" t="n"/>
-      <c r="P160" s="12" t="n"/>
-      <c r="Q160" s="28" t="n"/>
-      <c r="R160" s="12" t="n"/>
+      <c r="P160" s="28" t="n"/>
+      <c r="Q160" s="12" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="12" t="inlineStr">
@@ -20079,7 +19484,7 @@
       </c>
       <c r="K161" s="12" t="inlineStr">
         <is>
-          <t>No Delete action; the call to delete an attachment of the case is refused.</t>
+          <t>No Delete action; a direct request to delete an attachment of the case is refused.</t>
         </is>
       </c>
       <c r="L161" s="12" t="inlineStr">
@@ -20087,16 +19492,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M161" s="12" t="inlineStr"/>
-      <c r="N161" s="27" t="inlineStr">
+      <c r="M161" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N161" s="12" t="n"/>
       <c r="O161" s="12" t="n"/>
-      <c r="P161" s="12" t="n"/>
-      <c r="Q161" s="28" t="n"/>
-      <c r="R161" s="12" t="n"/>
+      <c r="P161" s="28" t="n"/>
+      <c r="Q161" s="12" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="12" t="inlineStr">
@@ -20160,16 +19564,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M162" s="12" t="inlineStr"/>
-      <c r="N162" s="27" t="inlineStr">
+      <c r="M162" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N162" s="12" t="n"/>
       <c r="O162" s="12" t="n"/>
-      <c r="P162" s="12" t="n"/>
-      <c r="Q162" s="28" t="n"/>
-      <c r="R162" s="12" t="n"/>
+      <c r="P162" s="28" t="n"/>
+      <c r="Q162" s="12" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="12" t="inlineStr">
@@ -20232,16 +19635,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M163" s="12" t="inlineStr"/>
-      <c r="N163" s="27" t="inlineStr">
+      <c r="M163" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N163" s="12" t="n"/>
       <c r="O163" s="12" t="n"/>
-      <c r="P163" s="12" t="n"/>
-      <c r="Q163" s="28" t="n"/>
-      <c r="R163" s="12" t="n"/>
+      <c r="P163" s="28" t="n"/>
+      <c r="Q163" s="12" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="12" t="inlineStr">
@@ -20306,16 +19708,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M164" s="12" t="inlineStr"/>
-      <c r="N164" s="27" t="inlineStr">
+      <c r="M164" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N164" s="12" t="n"/>
       <c r="O164" s="12" t="n"/>
-      <c r="P164" s="12" t="n"/>
-      <c r="Q164" s="28" t="n"/>
-      <c r="R164" s="12" t="n"/>
+      <c r="P164" s="28" t="n"/>
+      <c r="Q164" s="12" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="12" t="inlineStr">
@@ -20379,16 +19780,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M165" s="12" t="inlineStr"/>
-      <c r="N165" s="27" t="inlineStr">
+      <c r="M165" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N165" s="12" t="n"/>
       <c r="O165" s="12" t="n"/>
-      <c r="P165" s="12" t="n"/>
-      <c r="Q165" s="28" t="n"/>
-      <c r="R165" s="12" t="n"/>
+      <c r="P165" s="28" t="n"/>
+      <c r="Q165" s="12" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="12" t="inlineStr">
@@ -20451,16 +19851,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M166" s="12" t="inlineStr"/>
-      <c r="N166" s="27" t="inlineStr">
+      <c r="M166" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N166" s="12" t="n"/>
       <c r="O166" s="12" t="n"/>
-      <c r="P166" s="12" t="n"/>
-      <c r="Q166" s="28" t="n"/>
-      <c r="R166" s="12" t="n"/>
+      <c r="P166" s="28" t="n"/>
+      <c r="Q166" s="12" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="12" t="inlineStr">
@@ -20524,16 +19923,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M167" s="12" t="inlineStr"/>
-      <c r="N167" s="27" t="inlineStr">
+      <c r="M167" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N167" s="12" t="n"/>
       <c r="O167" s="12" t="n"/>
-      <c r="P167" s="12" t="n"/>
-      <c r="Q167" s="28" t="n"/>
-      <c r="R167" s="12" t="n"/>
+      <c r="P167" s="28" t="n"/>
+      <c r="Q167" s="12" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="12" t="inlineStr">
@@ -20597,16 +19995,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M168" s="12" t="inlineStr"/>
-      <c r="N168" s="27" t="inlineStr">
+      <c r="M168" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N168" s="12" t="n"/>
       <c r="O168" s="12" t="n"/>
-      <c r="P168" s="12" t="n"/>
-      <c r="Q168" s="28" t="n"/>
-      <c r="R168" s="12" t="n"/>
+      <c r="P168" s="28" t="n"/>
+      <c r="Q168" s="12" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="12" t="inlineStr">
@@ -20671,16 +20068,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M169" s="12" t="inlineStr"/>
-      <c r="N169" s="27" t="inlineStr">
+      <c r="M169" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N169" s="12" t="n"/>
       <c r="O169" s="12" t="n"/>
-      <c r="P169" s="12" t="n"/>
-      <c r="Q169" s="28" t="n"/>
-      <c r="R169" s="12" t="n"/>
+      <c r="P169" s="28" t="n"/>
+      <c r="Q169" s="12" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="12" t="inlineStr">
@@ -20743,16 +20139,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M170" s="12" t="inlineStr"/>
-      <c r="N170" s="27" t="inlineStr">
+      <c r="M170" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N170" s="12" t="n"/>
       <c r="O170" s="12" t="n"/>
-      <c r="P170" s="12" t="n"/>
-      <c r="Q170" s="28" t="n"/>
-      <c r="R170" s="12" t="n"/>
+      <c r="P170" s="28" t="n"/>
+      <c r="Q170" s="12" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="12" t="inlineStr">
@@ -20815,16 +20210,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M171" s="12" t="inlineStr"/>
-      <c r="N171" s="27" t="inlineStr">
+      <c r="M171" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N171" s="12" t="n"/>
       <c r="O171" s="12" t="n"/>
-      <c r="P171" s="12" t="n"/>
-      <c r="Q171" s="28" t="n"/>
-      <c r="R171" s="12" t="n"/>
+      <c r="P171" s="28" t="n"/>
+      <c r="Q171" s="12" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="12" t="inlineStr">
@@ -20888,16 +20282,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M172" s="12" t="inlineStr"/>
-      <c r="N172" s="27" t="inlineStr">
+      <c r="M172" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N172" s="12" t="n"/>
       <c r="O172" s="12" t="n"/>
-      <c r="P172" s="12" t="n"/>
-      <c r="Q172" s="28" t="n"/>
-      <c r="R172" s="12" t="n"/>
+      <c r="P172" s="28" t="n"/>
+      <c r="Q172" s="12" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="12" t="inlineStr">
@@ -20960,16 +20353,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M173" s="12" t="inlineStr"/>
-      <c r="N173" s="27" t="inlineStr">
+      <c r="M173" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N173" s="12" t="n"/>
       <c r="O173" s="12" t="n"/>
-      <c r="P173" s="12" t="n"/>
-      <c r="Q173" s="28" t="n"/>
-      <c r="R173" s="12" t="n"/>
+      <c r="P173" s="28" t="n"/>
+      <c r="Q173" s="12" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="12" t="inlineStr">
@@ -21032,16 +20424,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M174" s="12" t="inlineStr"/>
-      <c r="N174" s="27" t="inlineStr">
+      <c r="M174" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N174" s="12" t="n"/>
       <c r="O174" s="12" t="n"/>
-      <c r="P174" s="12" t="n"/>
-      <c r="Q174" s="28" t="n"/>
-      <c r="R174" s="12" t="n"/>
+      <c r="P174" s="28" t="n"/>
+      <c r="Q174" s="12" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="12" t="inlineStr">
@@ -21105,16 +20496,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M175" s="12" t="inlineStr"/>
-      <c r="N175" s="27" t="inlineStr">
+      <c r="M175" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N175" s="12" t="n"/>
       <c r="O175" s="12" t="n"/>
-      <c r="P175" s="12" t="n"/>
-      <c r="Q175" s="28" t="n"/>
-      <c r="R175" s="12" t="n"/>
+      <c r="P175" s="28" t="n"/>
+      <c r="Q175" s="12" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="12" t="inlineStr">
@@ -21178,16 +20568,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M176" s="12" t="inlineStr"/>
-      <c r="N176" s="27" t="inlineStr">
+      <c r="M176" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N176" s="12" t="n"/>
       <c r="O176" s="12" t="n"/>
-      <c r="P176" s="12" t="n"/>
-      <c r="Q176" s="28" t="n"/>
-      <c r="R176" s="12" t="n"/>
+      <c r="P176" s="28" t="n"/>
+      <c r="Q176" s="12" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="12" t="inlineStr">
@@ -21251,16 +20640,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M177" s="12" t="inlineStr"/>
-      <c r="N177" s="27" t="inlineStr">
+      <c r="M177" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N177" s="12" t="n"/>
       <c r="O177" s="12" t="n"/>
-      <c r="P177" s="12" t="n"/>
-      <c r="Q177" s="28" t="n"/>
-      <c r="R177" s="12" t="n"/>
+      <c r="P177" s="28" t="n"/>
+      <c r="Q177" s="12" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="12" t="inlineStr">
@@ -21323,16 +20711,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M178" s="12" t="inlineStr"/>
-      <c r="N178" s="27" t="inlineStr">
+      <c r="M178" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N178" s="12" t="n"/>
       <c r="O178" s="12" t="n"/>
-      <c r="P178" s="12" t="n"/>
-      <c r="Q178" s="28" t="n"/>
-      <c r="R178" s="12" t="n"/>
+      <c r="P178" s="28" t="n"/>
+      <c r="Q178" s="12" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="12" t="inlineStr">
@@ -21395,16 +20782,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M179" s="12" t="inlineStr"/>
-      <c r="N179" s="27" t="inlineStr">
+      <c r="M179" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N179" s="12" t="n"/>
       <c r="O179" s="12" t="n"/>
-      <c r="P179" s="12" t="n"/>
-      <c r="Q179" s="28" t="n"/>
-      <c r="R179" s="12" t="n"/>
+      <c r="P179" s="28" t="n"/>
+      <c r="Q179" s="12" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="12" t="inlineStr">
@@ -21467,16 +20853,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M180" s="12" t="inlineStr"/>
-      <c r="N180" s="27" t="inlineStr">
+      <c r="M180" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N180" s="12" t="n"/>
       <c r="O180" s="12" t="n"/>
-      <c r="P180" s="12" t="n"/>
-      <c r="Q180" s="28" t="n"/>
-      <c r="R180" s="12" t="n"/>
+      <c r="P180" s="28" t="n"/>
+      <c r="Q180" s="12" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="12" t="inlineStr">
@@ -21540,16 +20925,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M181" s="12" t="inlineStr"/>
-      <c r="N181" s="27" t="inlineStr">
+      <c r="M181" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N181" s="12" t="n"/>
       <c r="O181" s="12" t="n"/>
-      <c r="P181" s="12" t="n"/>
-      <c r="Q181" s="28" t="n"/>
-      <c r="R181" s="12" t="n"/>
+      <c r="P181" s="28" t="n"/>
+      <c r="Q181" s="12" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="12" t="inlineStr">
@@ -21612,16 +20996,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M182" s="12" t="inlineStr"/>
-      <c r="N182" s="27" t="inlineStr">
+      <c r="M182" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N182" s="12" t="n"/>
       <c r="O182" s="12" t="n"/>
-      <c r="P182" s="12" t="n"/>
-      <c r="Q182" s="28" t="n"/>
-      <c r="R182" s="12" t="n"/>
+      <c r="P182" s="28" t="n"/>
+      <c r="Q182" s="12" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="12" t="inlineStr">
@@ -21685,16 +21068,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M183" s="12" t="inlineStr"/>
-      <c r="N183" s="27" t="inlineStr">
+      <c r="M183" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N183" s="12" t="n"/>
       <c r="O183" s="12" t="n"/>
-      <c r="P183" s="12" t="n"/>
-      <c r="Q183" s="28" t="n"/>
-      <c r="R183" s="12" t="n"/>
+      <c r="P183" s="28" t="n"/>
+      <c r="Q183" s="12" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="12" t="inlineStr">
@@ -21757,16 +21139,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M184" s="12" t="inlineStr"/>
-      <c r="N184" s="27" t="inlineStr">
+      <c r="M184" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N184" s="12" t="n"/>
       <c r="O184" s="12" t="n"/>
-      <c r="P184" s="12" t="n"/>
-      <c r="Q184" s="28" t="n"/>
-      <c r="R184" s="12" t="n"/>
+      <c r="P184" s="28" t="n"/>
+      <c r="Q184" s="12" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="12" t="inlineStr">
@@ -21829,16 +21210,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M185" s="12" t="inlineStr"/>
-      <c r="N185" s="27" t="inlineStr">
+      <c r="M185" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N185" s="12" t="n"/>
       <c r="O185" s="12" t="n"/>
-      <c r="P185" s="12" t="n"/>
-      <c r="Q185" s="28" t="n"/>
-      <c r="R185" s="12" t="n"/>
+      <c r="P185" s="28" t="n"/>
+      <c r="Q185" s="12" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="12" t="inlineStr">
@@ -21902,16 +21282,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M186" s="12" t="inlineStr"/>
-      <c r="N186" s="27" t="inlineStr">
+      <c r="M186" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N186" s="12" t="n"/>
       <c r="O186" s="12" t="n"/>
-      <c r="P186" s="12" t="n"/>
-      <c r="Q186" s="28" t="n"/>
-      <c r="R186" s="12" t="n"/>
+      <c r="P186" s="28" t="n"/>
+      <c r="Q186" s="12" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="12" t="inlineStr">
@@ -21975,16 +21354,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M187" s="12" t="inlineStr"/>
-      <c r="N187" s="27" t="inlineStr">
+      <c r="M187" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N187" s="12" t="n"/>
       <c r="O187" s="12" t="n"/>
-      <c r="P187" s="12" t="n"/>
-      <c r="Q187" s="28" t="n"/>
-      <c r="R187" s="12" t="n"/>
+      <c r="P187" s="28" t="n"/>
+      <c r="Q187" s="12" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="12" t="inlineStr">
@@ -22048,16 +21426,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M188" s="12" t="inlineStr"/>
-      <c r="N188" s="27" t="inlineStr">
+      <c r="M188" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N188" s="12" t="n"/>
       <c r="O188" s="12" t="n"/>
-      <c r="P188" s="12" t="n"/>
-      <c r="Q188" s="28" t="n"/>
-      <c r="R188" s="12" t="n"/>
+      <c r="P188" s="28" t="n"/>
+      <c r="Q188" s="12" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="12" t="inlineStr">
@@ -22120,16 +21497,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M189" s="12" t="inlineStr"/>
-      <c r="N189" s="27" t="inlineStr">
+      <c r="M189" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N189" s="12" t="n"/>
       <c r="O189" s="12" t="n"/>
-      <c r="P189" s="12" t="n"/>
-      <c r="Q189" s="28" t="n"/>
-      <c r="R189" s="12" t="n"/>
+      <c r="P189" s="28" t="n"/>
+      <c r="Q189" s="12" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="12" t="inlineStr">
@@ -22192,16 +21568,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M190" s="12" t="inlineStr"/>
-      <c r="N190" s="27" t="inlineStr">
+      <c r="M190" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N190" s="12" t="n"/>
       <c r="O190" s="12" t="n"/>
-      <c r="P190" s="12" t="n"/>
-      <c r="Q190" s="28" t="n"/>
-      <c r="R190" s="12" t="n"/>
+      <c r="P190" s="28" t="n"/>
+      <c r="Q190" s="12" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="12" t="inlineStr">
@@ -22264,16 +21639,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M191" s="12" t="inlineStr"/>
-      <c r="N191" s="27" t="inlineStr">
+      <c r="M191" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N191" s="12" t="n"/>
       <c r="O191" s="12" t="n"/>
-      <c r="P191" s="12" t="n"/>
-      <c r="Q191" s="28" t="n"/>
-      <c r="R191" s="12" t="n"/>
+      <c r="P191" s="28" t="n"/>
+      <c r="Q191" s="12" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="12" t="inlineStr">
@@ -22337,16 +21711,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M192" s="12" t="inlineStr"/>
-      <c r="N192" s="27" t="inlineStr">
+      <c r="M192" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N192" s="12" t="n"/>
       <c r="O192" s="12" t="n"/>
-      <c r="P192" s="12" t="n"/>
-      <c r="Q192" s="28" t="n"/>
-      <c r="R192" s="12" t="n"/>
+      <c r="P192" s="28" t="n"/>
+      <c r="Q192" s="12" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="12" t="inlineStr">
@@ -22410,16 +21783,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M193" s="12" t="inlineStr"/>
-      <c r="N193" s="27" t="inlineStr">
+      <c r="M193" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N193" s="12" t="n"/>
       <c r="O193" s="12" t="n"/>
-      <c r="P193" s="12" t="n"/>
-      <c r="Q193" s="28" t="n"/>
-      <c r="R193" s="12" t="n"/>
+      <c r="P193" s="28" t="n"/>
+      <c r="Q193" s="12" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="12" t="inlineStr">
@@ -22482,16 +21854,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M194" s="12" t="inlineStr"/>
-      <c r="N194" s="27" t="inlineStr">
+      <c r="M194" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N194" s="12" t="n"/>
       <c r="O194" s="12" t="n"/>
-      <c r="P194" s="12" t="n"/>
-      <c r="Q194" s="28" t="n"/>
-      <c r="R194" s="12" t="n"/>
+      <c r="P194" s="28" t="n"/>
+      <c r="Q194" s="12" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="12" t="inlineStr">
@@ -22554,16 +21925,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M195" s="12" t="inlineStr"/>
-      <c r="N195" s="27" t="inlineStr">
+      <c r="M195" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N195" s="12" t="n"/>
       <c r="O195" s="12" t="n"/>
-      <c r="P195" s="12" t="n"/>
-      <c r="Q195" s="28" t="n"/>
-      <c r="R195" s="12" t="n"/>
+      <c r="P195" s="28" t="n"/>
+      <c r="Q195" s="12" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="12" t="inlineStr">
@@ -22627,16 +21997,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M196" s="12" t="inlineStr"/>
-      <c r="N196" s="27" t="inlineStr">
+      <c r="M196" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N196" s="12" t="n"/>
       <c r="O196" s="12" t="n"/>
-      <c r="P196" s="12" t="n"/>
-      <c r="Q196" s="28" t="n"/>
-      <c r="R196" s="12" t="n"/>
+      <c r="P196" s="28" t="n"/>
+      <c r="Q196" s="12" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="12" t="inlineStr">
@@ -22700,16 +22069,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M197" s="12" t="inlineStr"/>
-      <c r="N197" s="27" t="inlineStr">
+      <c r="M197" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N197" s="12" t="n"/>
       <c r="O197" s="12" t="n"/>
-      <c r="P197" s="12" t="n"/>
-      <c r="Q197" s="28" t="n"/>
-      <c r="R197" s="12" t="n"/>
+      <c r="P197" s="28" t="n"/>
+      <c r="Q197" s="12" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="12" t="inlineStr">
@@ -22772,16 +22140,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M198" s="12" t="inlineStr"/>
-      <c r="N198" s="27" t="inlineStr">
+      <c r="M198" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N198" s="12" t="n"/>
       <c r="O198" s="12" t="n"/>
-      <c r="P198" s="12" t="n"/>
-      <c r="Q198" s="28" t="n"/>
-      <c r="R198" s="12" t="n"/>
+      <c r="P198" s="28" t="n"/>
+      <c r="Q198" s="12" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="12" t="inlineStr">
@@ -22844,16 +22211,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M199" s="12" t="inlineStr"/>
-      <c r="N199" s="27" t="inlineStr">
+      <c r="M199" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N199" s="12" t="n"/>
       <c r="O199" s="12" t="n"/>
-      <c r="P199" s="12" t="n"/>
-      <c r="Q199" s="28" t="n"/>
-      <c r="R199" s="12" t="n"/>
+      <c r="P199" s="28" t="n"/>
+      <c r="Q199" s="12" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="12" t="inlineStr">
@@ -22916,16 +22282,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M200" s="12" t="inlineStr"/>
-      <c r="N200" s="27" t="inlineStr">
+      <c r="M200" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N200" s="12" t="n"/>
       <c r="O200" s="12" t="n"/>
-      <c r="P200" s="12" t="n"/>
-      <c r="Q200" s="28" t="n"/>
-      <c r="R200" s="12" t="n"/>
+      <c r="P200" s="28" t="n"/>
+      <c r="Q200" s="12" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="12" t="inlineStr">
@@ -22988,16 +22353,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M201" s="12" t="inlineStr"/>
-      <c r="N201" s="27" t="inlineStr">
+      <c r="M201" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N201" s="12" t="n"/>
       <c r="O201" s="12" t="n"/>
-      <c r="P201" s="12" t="n"/>
-      <c r="Q201" s="28" t="n"/>
-      <c r="R201" s="12" t="n"/>
+      <c r="P201" s="28" t="n"/>
+      <c r="Q201" s="12" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="12" t="inlineStr">
@@ -23061,16 +22425,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M202" s="12" t="inlineStr"/>
-      <c r="N202" s="27" t="inlineStr">
+      <c r="M202" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N202" s="12" t="n"/>
       <c r="O202" s="12" t="n"/>
-      <c r="P202" s="12" t="n"/>
-      <c r="Q202" s="28" t="n"/>
-      <c r="R202" s="12" t="n"/>
+      <c r="P202" s="28" t="n"/>
+      <c r="Q202" s="12" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="12" t="inlineStr">
@@ -23133,16 +22496,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M203" s="12" t="inlineStr"/>
-      <c r="N203" s="27" t="inlineStr">
+      <c r="M203" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N203" s="12" t="n"/>
       <c r="O203" s="12" t="n"/>
-      <c r="P203" s="12" t="n"/>
-      <c r="Q203" s="28" t="n"/>
-      <c r="R203" s="12" t="n"/>
+      <c r="P203" s="28" t="n"/>
+      <c r="Q203" s="12" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="12" t="inlineStr">
@@ -23205,16 +22567,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M204" s="12" t="inlineStr"/>
-      <c r="N204" s="27" t="inlineStr">
+      <c r="M204" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N204" s="12" t="n"/>
       <c r="O204" s="12" t="n"/>
-      <c r="P204" s="12" t="n"/>
-      <c r="Q204" s="28" t="n"/>
-      <c r="R204" s="12" t="n"/>
+      <c r="P204" s="28" t="n"/>
+      <c r="Q204" s="12" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="12" t="inlineStr">
@@ -23277,16 +22638,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M205" s="12" t="inlineStr"/>
-      <c r="N205" s="27" t="inlineStr">
+      <c r="M205" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N205" s="12" t="n"/>
       <c r="O205" s="12" t="n"/>
-      <c r="P205" s="12" t="n"/>
-      <c r="Q205" s="28" t="n"/>
-      <c r="R205" s="12" t="n"/>
+      <c r="P205" s="28" t="n"/>
+      <c r="Q205" s="12" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="12" t="inlineStr">
@@ -23349,16 +22709,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M206" s="12" t="inlineStr"/>
-      <c r="N206" s="27" t="inlineStr">
+      <c r="M206" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N206" s="12" t="n"/>
       <c r="O206" s="12" t="n"/>
-      <c r="P206" s="12" t="n"/>
-      <c r="Q206" s="28" t="n"/>
-      <c r="R206" s="12" t="n"/>
+      <c r="P206" s="28" t="n"/>
+      <c r="Q206" s="12" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="12" t="inlineStr">
@@ -23421,16 +22780,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M207" s="12" t="inlineStr"/>
-      <c r="N207" s="27" t="inlineStr">
+      <c r="M207" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N207" s="12" t="n"/>
       <c r="O207" s="12" t="n"/>
-      <c r="P207" s="12" t="n"/>
-      <c r="Q207" s="28" t="n"/>
-      <c r="R207" s="12" t="n"/>
+      <c r="P207" s="28" t="n"/>
+      <c r="Q207" s="12" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="12" t="inlineStr">
@@ -23493,16 +22851,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M208" s="12" t="inlineStr"/>
-      <c r="N208" s="27" t="inlineStr">
+      <c r="M208" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N208" s="12" t="n"/>
       <c r="O208" s="12" t="n"/>
-      <c r="P208" s="12" t="n"/>
-      <c r="Q208" s="28" t="n"/>
-      <c r="R208" s="12" t="n"/>
+      <c r="P208" s="28" t="n"/>
+      <c r="Q208" s="12" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="12" t="inlineStr">
@@ -23565,16 +22922,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M209" s="12" t="inlineStr"/>
-      <c r="N209" s="27" t="inlineStr">
+      <c r="M209" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N209" s="12" t="n"/>
       <c r="O209" s="12" t="n"/>
-      <c r="P209" s="12" t="n"/>
-      <c r="Q209" s="28" t="n"/>
-      <c r="R209" s="12" t="n"/>
+      <c r="P209" s="28" t="n"/>
+      <c r="Q209" s="12" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="12" t="inlineStr">
@@ -23624,12 +22980,12 @@
       </c>
       <c r="J210" s="12" t="inlineStr">
         <is>
-          <t>1. As investigator open Reports; call the run of SCR-CASE-STATUS.</t>
+          <t>1. As investigator open Reports; send a direct request to run SCR-CASE-STATUS.</t>
         </is>
       </c>
       <c r="K210" s="12" t="inlineStr">
         <is>
-          <t>The Compliance category is not listed; the call returns HTTP 403.
+          <t>The Compliance category is not listed; the request is refused.
 Message "You are not permitted to perform this action".</t>
         </is>
       </c>
@@ -23638,16 +22994,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M210" s="12" t="inlineStr"/>
-      <c r="N210" s="27" t="inlineStr">
+      <c r="M210" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N210" s="12" t="n"/>
       <c r="O210" s="12" t="n"/>
-      <c r="P210" s="12" t="n"/>
-      <c r="Q210" s="28" t="n"/>
-      <c r="R210" s="12" t="n"/>
+      <c r="P210" s="28" t="n"/>
+      <c r="Q210" s="12" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="12" t="inlineStr">
@@ -23711,16 +23066,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M211" s="12" t="inlineStr"/>
-      <c r="N211" s="27" t="inlineStr">
+      <c r="M211" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N211" s="12" t="n"/>
       <c r="O211" s="12" t="n"/>
-      <c r="P211" s="12" t="n"/>
-      <c r="Q211" s="28" t="n"/>
-      <c r="R211" s="12" t="n"/>
+      <c r="P211" s="28" t="n"/>
+      <c r="Q211" s="12" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="12" t="inlineStr">
@@ -23783,16 +23137,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M212" s="12" t="inlineStr"/>
-      <c r="N212" s="27" t="inlineStr">
+      <c r="M212" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N212" s="12" t="n"/>
       <c r="O212" s="12" t="n"/>
-      <c r="P212" s="12" t="n"/>
-      <c r="Q212" s="28" t="n"/>
-      <c r="R212" s="12" t="n"/>
+      <c r="P212" s="28" t="n"/>
+      <c r="Q212" s="12" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="12" t="inlineStr">
@@ -23842,12 +23195,12 @@
       </c>
       <c r="J213" s="12" t="inlineStr">
         <is>
-          <t>1. Open an audit row and a timeline event; look for edit and delete; call delete through the API.</t>
+          <t>1. Open an audit row and a timeline event; look for edit and delete; send a direct request to delete them.</t>
         </is>
       </c>
       <c r="K213" s="12" t="inlineStr">
         <is>
-          <t>No action offered; the API offers no update or delete and the call is refused.</t>
+          <t>No action offered; no update or delete is offered and direct requests are refused.</t>
         </is>
       </c>
       <c r="L213" s="12" t="inlineStr">
@@ -23855,16 +23208,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M213" s="12" t="inlineStr"/>
-      <c r="N213" s="27" t="inlineStr">
+      <c r="M213" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N213" s="12" t="n"/>
       <c r="O213" s="12" t="n"/>
-      <c r="P213" s="12" t="n"/>
-      <c r="Q213" s="28" t="n"/>
-      <c r="R213" s="12" t="n"/>
+      <c r="P213" s="28" t="n"/>
+      <c r="Q213" s="12" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="12" t="inlineStr">
@@ -23927,16 +23279,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M214" s="12" t="inlineStr"/>
-      <c r="N214" s="27" t="inlineStr">
+      <c r="M214" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N214" s="12" t="n"/>
       <c r="O214" s="12" t="n"/>
-      <c r="P214" s="12" t="n"/>
-      <c r="Q214" s="28" t="n"/>
-      <c r="R214" s="12" t="n"/>
+      <c r="P214" s="28" t="n"/>
+      <c r="Q214" s="12" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="12" t="inlineStr">
@@ -23999,16 +23350,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M215" s="12" t="inlineStr"/>
-      <c r="N215" s="27" t="inlineStr">
+      <c r="M215" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N215" s="12" t="n"/>
       <c r="O215" s="12" t="n"/>
-      <c r="P215" s="12" t="n"/>
-      <c r="Q215" s="28" t="n"/>
-      <c r="R215" s="12" t="n"/>
+      <c r="P215" s="28" t="n"/>
+      <c r="Q215" s="12" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="12" t="inlineStr">
@@ -24071,16 +23421,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M216" s="12" t="inlineStr"/>
-      <c r="N216" s="27" t="inlineStr">
+      <c r="M216" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N216" s="12" t="n"/>
       <c r="O216" s="12" t="n"/>
-      <c r="P216" s="12" t="n"/>
-      <c r="Q216" s="28" t="n"/>
-      <c r="R216" s="12" t="n"/>
+      <c r="P216" s="28" t="n"/>
+      <c r="Q216" s="12" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="12" t="inlineStr">
@@ -24130,12 +23479,12 @@
       </c>
       <c r="J217" s="12" t="inlineStr">
         <is>
-          <t>1. As ucc call the run of SCR-AUDIT-LOG.</t>
+          <t>1. As ucc send a direct request to run SCR-AUDIT-LOG.</t>
         </is>
       </c>
       <c r="K217" s="12" t="inlineStr">
         <is>
-          <t>HTTP 403.
+          <t>A direct request is refused with "You are not permitted to perform this action".
 Message "You are not permitted to perform this action".</t>
         </is>
       </c>
@@ -24144,16 +23493,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M217" s="12" t="inlineStr"/>
-      <c r="N217" s="27" t="inlineStr">
+      <c r="M217" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N217" s="12" t="n"/>
       <c r="O217" s="12" t="n"/>
-      <c r="P217" s="12" t="n"/>
-      <c r="Q217" s="28" t="n"/>
-      <c r="R217" s="12" t="n"/>
+      <c r="P217" s="28" t="n"/>
+      <c r="Q217" s="12" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="12" t="inlineStr">
@@ -24217,23 +23565,22 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M218" s="12" t="inlineStr"/>
-      <c r="N218" s="27" t="inlineStr">
+      <c r="M218" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N218" s="12" t="n"/>
       <c r="O218" s="12" t="n"/>
-      <c r="P218" s="12" t="n"/>
-      <c r="Q218" s="28" t="n"/>
-      <c r="R218" s="12" t="n"/>
+      <c r="P218" s="28" t="n"/>
+      <c r="Q218" s="12" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:R218"/>
+  <autoFilter ref="A4:Q218"/>
   <mergeCells count="1">
-    <mergeCell ref="A2:R2"/>
+    <mergeCell ref="A2:Q2"/>
   </mergeCells>
-  <conditionalFormatting sqref="N5:N718">
+  <conditionalFormatting sqref="M5:M718">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="1" stopIfTrue="1">
       <formula>"Pass"</formula>
     </cfRule>
@@ -24247,19 +23594,19 @@
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A5:R718">
+  <conditionalFormatting sqref="A5:Q718">
     <cfRule type="expression" priority="5" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
     <dataValidation sqref="F5:F718" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Type" error="Choose a value from the list (Type)." type="list">
-      <formula1>'_lists'!$B$1:$B$7</formula1>
+      <formula1>'_lists'!$B$1:$B$9</formula1>
     </dataValidation>
     <dataValidation sqref="L5:L718" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Priority" error="Choose a value from the list (Priority)." type="list">
       <formula1>'_lists'!$C$1:$C$3</formula1>
     </dataValidation>
-    <dataValidation sqref="N5:N718" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Status" error="Choose a value from the list (Status)." type="list">
+    <dataValidation sqref="M5:M718" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Status" error="Choose a value from the list (Status)." type="list">
       <formula1>'_lists'!$D$1:$D$5</formula1>
     </dataValidation>
   </dataValidations>
@@ -24283,7 +23630,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J90"/>
+  <dimension ref="A1:I90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -24295,7 +23642,6 @@
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -24322,7 +23668,6 @@
       <c r="G3" s="25" t="n"/>
       <c r="H3" s="25" t="n"/>
       <c r="I3" s="25" t="n"/>
-      <c r="J3" s="25" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="26" t="inlineStr">
@@ -24367,11 +23712,6 @@
       </c>
       <c r="I4" s="26" t="inlineStr">
         <is>
-          <t>Automated</t>
-        </is>
-      </c>
-      <c r="J4" s="26" t="inlineStr">
-        <is>
           <t>Coverage</t>
         </is>
       </c>
@@ -24409,10 +23749,7 @@
       <c r="H5" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="I5" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="27" t="inlineStr">
+      <c r="I5" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24451,10 +23788,7 @@
       <c r="H6" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="I6" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="27" t="inlineStr">
+      <c r="I6" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24493,10 +23827,7 @@
       <c r="H7" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I7" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="27" t="inlineStr">
+      <c r="I7" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24535,10 +23866,7 @@
       <c r="H8" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I8" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="27" t="inlineStr">
+      <c r="I8" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24577,10 +23905,7 @@
       <c r="H9" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="I9" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="27" t="inlineStr">
+      <c r="I9" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24619,10 +23944,7 @@
       <c r="H10" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="I10" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="27" t="inlineStr">
+      <c r="I10" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24661,10 +23983,7 @@
       <c r="H11" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I11" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="27" t="inlineStr">
+      <c r="I11" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24703,10 +24022,7 @@
       <c r="H12" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I12" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="27" t="inlineStr">
+      <c r="I12" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24745,10 +24061,7 @@
       <c r="H13" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I13" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="27" t="inlineStr">
+      <c r="I13" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24787,10 +24100,7 @@
       <c r="H14" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I14" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="27" t="inlineStr">
+      <c r="I14" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24829,10 +24139,7 @@
       <c r="H15" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="27" t="inlineStr">
+      <c r="I15" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24871,10 +24178,7 @@
       <c r="H16" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I16" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="27" t="inlineStr">
+      <c r="I16" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24913,10 +24217,7 @@
       <c r="H17" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I17" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="27" t="inlineStr">
+      <c r="I17" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24955,10 +24256,7 @@
       <c r="H18" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I18" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="27" t="inlineStr">
+      <c r="I18" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24997,10 +24295,7 @@
       <c r="H19" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I19" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="27" t="inlineStr">
+      <c r="I19" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -25039,10 +24334,7 @@
       <c r="H20" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="I20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="27" t="inlineStr">
+      <c r="I20" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -25081,10 +24373,7 @@
       <c r="H21" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="27" t="inlineStr">
+      <c r="I21" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -25123,10 +24412,7 @@
       <c r="H22" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I22" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="27" t="inlineStr">
+      <c r="I22" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -25165,10 +24451,7 @@
       <c r="H23" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I23" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="27" t="inlineStr">
+      <c r="I23" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -25207,10 +24490,7 @@
       <c r="H24" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I24" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="27" t="inlineStr">
+      <c r="I24" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -25249,10 +24529,7 @@
       <c r="H25" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I25" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="27" t="inlineStr">
+      <c r="I25" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -25291,10 +24568,7 @@
       <c r="H26" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I26" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="27" t="inlineStr">
+      <c r="I26" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -25333,10 +24607,7 @@
       <c r="H27" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I27" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="27" t="inlineStr">
+      <c r="I27" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -25375,10 +24646,7 @@
       <c r="H28" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I28" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" s="27" t="inlineStr">
+      <c r="I28" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -25417,10 +24685,7 @@
       <c r="H29" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I29" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="27" t="inlineStr">
+      <c r="I29" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -25459,10 +24724,7 @@
       <c r="H30" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I30" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="27" t="inlineStr">
+      <c r="I30" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -25501,10 +24763,7 @@
       <c r="H31" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I31" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" s="27" t="inlineStr">
+      <c r="I31" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -25543,10 +24802,7 @@
       <c r="H32" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I32" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="27" t="inlineStr">
+      <c r="I32" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -25585,10 +24841,7 @@
       <c r="H33" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I33" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" s="27" t="inlineStr">
+      <c r="I33" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -25627,10 +24880,7 @@
       <c r="H34" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I34" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="27" t="inlineStr">
+      <c r="I34" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -25669,10 +24919,7 @@
       <c r="H35" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I35" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" s="27" t="inlineStr">
+      <c r="I35" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -25711,10 +24958,7 @@
       <c r="H36" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I36" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" s="27" t="inlineStr">
+      <c r="I36" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -25753,10 +24997,7 @@
       <c r="H37" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I37" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" s="27" t="inlineStr">
+      <c r="I37" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -25795,10 +25036,7 @@
       <c r="H38" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I38" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" s="27" t="inlineStr">
+      <c r="I38" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -25837,10 +25075,7 @@
       <c r="H39" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I39" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" s="27" t="inlineStr">
+      <c r="I39" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -25879,10 +25114,7 @@
       <c r="H40" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I40" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" s="27" t="inlineStr">
+      <c r="I40" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -25921,10 +25153,7 @@
       <c r="H41" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I41" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="27" t="inlineStr">
+      <c r="I41" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -25963,10 +25192,7 @@
       <c r="H42" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I42" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" s="27" t="inlineStr">
+      <c r="I42" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -26005,10 +25231,7 @@
       <c r="H43" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I43" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" s="27" t="inlineStr">
+      <c r="I43" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -26047,10 +25270,7 @@
       <c r="H44" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I44" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" s="27" t="inlineStr">
+      <c r="I44" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -26089,10 +25309,7 @@
       <c r="H45" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I45" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" s="27" t="inlineStr">
+      <c r="I45" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -26131,10 +25348,7 @@
       <c r="H46" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I46" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" s="27" t="inlineStr">
+      <c r="I46" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -26173,10 +25387,7 @@
       <c r="H47" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I47" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" s="27" t="inlineStr">
+      <c r="I47" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -26215,10 +25426,7 @@
       <c r="H48" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I48" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" s="27" t="inlineStr">
+      <c r="I48" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -26253,10 +25461,7 @@
       <c r="H49" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="I49" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" s="27" t="inlineStr">
+      <c r="I49" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -26291,10 +25496,7 @@
       <c r="H50" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="I50" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" s="27" t="inlineStr">
+      <c r="I50" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -26329,10 +25531,7 @@
       <c r="H51" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="I51" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" s="27" t="inlineStr">
+      <c r="I51" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -26367,10 +25566,7 @@
       <c r="H52" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="I52" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" s="27" t="inlineStr">
+      <c r="I52" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -26405,10 +25601,7 @@
       <c r="H53" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="I53" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" s="27" t="inlineStr">
+      <c r="I53" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -26443,10 +25636,7 @@
       <c r="H54" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="I54" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" s="27" t="inlineStr">
+      <c r="I54" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -26481,10 +25671,7 @@
       <c r="H55" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I55" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" s="27" t="inlineStr">
+      <c r="I55" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -26519,10 +25706,7 @@
       <c r="H56" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="I56" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" s="27" t="inlineStr">
+      <c r="I56" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -26557,10 +25741,7 @@
       <c r="H57" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I57" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J57" s="27" t="inlineStr">
+      <c r="I57" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -26595,10 +25776,7 @@
       <c r="H58" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="I58" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" s="27" t="inlineStr">
+      <c r="I58" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -26633,10 +25811,7 @@
       <c r="H59" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I59" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" s="27" t="inlineStr">
+      <c r="I59" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -26671,10 +25846,7 @@
       <c r="H60" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="I60" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" s="27" t="inlineStr">
+      <c r="I60" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -26709,10 +25881,7 @@
       <c r="H61" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I61" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J61" s="27" t="inlineStr">
+      <c r="I61" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -26747,10 +25916,7 @@
       <c r="H62" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="I62" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" s="27" t="inlineStr">
+      <c r="I62" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -26785,10 +25951,7 @@
       <c r="H63" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I63" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" s="27" t="inlineStr">
+      <c r="I63" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -26823,10 +25986,7 @@
       <c r="H64" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="I64" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J64" s="27" t="inlineStr">
+      <c r="I64" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -26861,10 +26021,7 @@
       <c r="H65" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="I65" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J65" s="27" t="inlineStr">
+      <c r="I65" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -26899,10 +26056,7 @@
       <c r="H66" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I66" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J66" s="27" t="inlineStr">
+      <c r="I66" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -26937,10 +26091,7 @@
       <c r="H67" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="I67" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J67" s="27" t="inlineStr">
+      <c r="I67" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -26975,10 +26126,7 @@
       <c r="H68" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="I68" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J68" s="27" t="inlineStr">
+      <c r="I68" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -27013,10 +26161,7 @@
       <c r="H69" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I69" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J69" s="27" t="inlineStr">
+      <c r="I69" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -27051,10 +26196,7 @@
       <c r="H70" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="I70" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J70" s="27" t="inlineStr">
+      <c r="I70" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -27089,10 +26231,7 @@
       <c r="H71" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I71" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" s="27" t="inlineStr">
+      <c r="I71" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -27127,10 +26266,7 @@
       <c r="H72" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I72" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J72" s="27" t="inlineStr">
+      <c r="I72" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -27165,10 +26301,7 @@
       <c r="H73" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I73" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" s="27" t="inlineStr">
+      <c r="I73" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -27203,10 +26336,7 @@
       <c r="H74" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="I74" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J74" s="27" t="inlineStr">
+      <c r="I74" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -27241,10 +26371,7 @@
       <c r="H75" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I75" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J75" s="27" t="inlineStr">
+      <c r="I75" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -27279,10 +26406,7 @@
       <c r="H76" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="I76" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J76" s="27" t="inlineStr">
+      <c r="I76" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -27317,10 +26441,7 @@
       <c r="H77" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="I77" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J77" s="27" t="inlineStr">
+      <c r="I77" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -27355,10 +26476,7 @@
       <c r="H78" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I78" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J78" s="27" t="inlineStr">
+      <c r="I78" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -27393,10 +26511,7 @@
       <c r="H79" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I79" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J79" s="27" t="inlineStr">
+      <c r="I79" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -27431,10 +26546,7 @@
       <c r="H80" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="I80" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J80" s="27" t="inlineStr">
+      <c r="I80" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -27469,10 +26581,7 @@
       <c r="H81" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I81" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J81" s="27" t="inlineStr">
+      <c r="I81" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -27507,10 +26616,7 @@
       <c r="H82" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I82" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J82" s="27" t="inlineStr">
+      <c r="I82" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -27545,10 +26651,7 @@
       <c r="H83" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I83" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J83" s="27" t="inlineStr">
+      <c r="I83" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -27583,10 +26686,7 @@
       <c r="H84" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I84" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J84" s="27" t="inlineStr">
+      <c r="I84" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -27621,10 +26721,7 @@
       <c r="H85" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I85" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J85" s="27" t="inlineStr">
+      <c r="I85" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -27659,10 +26756,7 @@
       <c r="H86" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I86" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J86" s="27" t="inlineStr">
+      <c r="I86" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -27697,10 +26791,7 @@
       <c r="H87" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I87" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J87" s="27" t="inlineStr">
+      <c r="I87" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -27735,10 +26826,7 @@
       <c r="H88" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I88" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J88" s="27" t="inlineStr">
+      <c r="I88" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -27773,10 +26861,7 @@
       <c r="H89" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I89" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J89" s="27" t="inlineStr">
+      <c r="I89" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -27811,32 +26896,29 @@
       <c r="H90" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I90" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J90" s="27" t="inlineStr">
+      <c r="I90" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:J90"/>
+  <autoFilter ref="A4:I90"/>
   <mergeCells count="1">
-    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A2:I2"/>
   </mergeCells>
-  <conditionalFormatting sqref="J5:J590">
+  <conditionalFormatting sqref="I5:I590">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="2" stopIfTrue="1">
       <formula>"GAP"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A5:J590">
+  <conditionalFormatting sqref="A5:I590">
     <cfRule type="expression" priority="2" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="J5:J590" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Coverage" error="Choose a value from the list (Coverage)." type="list">
+    <dataValidation sqref="I5:I590" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Coverage" error="Choose a value from the list (Coverage)." type="list">
       <formula1>'_lists'!$E$1:$E$2</formula1>
     </dataValidation>
   </dataValidations>
@@ -27936,7 +27018,7 @@
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>Planned seed V1950 (compoff, compchk, ucc, investigator, scrapprover, amlcom1, amlcom2); the others created by the test lead through User Access requests</t>
+          <t>Seed data (compoff, compchk, ucc, investigator, scrapprover, amlcom1, amlcom2); the others created by the test lead through User Access requests</t>
         </is>
       </c>
       <c r="E5" s="12" t="n">
@@ -27961,7 +27043,7 @@
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>Planned seed V1950 of the build design</t>
+          <t>Seed data</t>
         </is>
       </c>
       <c r="E6" s="12" t="n">
@@ -27986,7 +27068,7 @@
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>Planned seed V1951; invented names only</t>
+          <t>Seed data; invented names only</t>
         </is>
       </c>
       <c r="E7" s="12" t="n">
@@ -28036,7 +27118,7 @@
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Masked seed clients (V981) plus clients keyed in by the test lead on SIT</t>
+          <t>Masked seed clients plus clients keyed in by the test lead on SIT</t>
         </is>
       </c>
       <c r="E9" s="12" t="n">
@@ -28061,7 +27143,7 @@
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>Planned seed V1952 of the build design</t>
+          <t>Seed data</t>
         </is>
       </c>
       <c r="E10" s="12" t="n">
@@ -28111,7 +27193,7 @@
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>Parameters as delivered; users of TD-SS-01</t>
+          <t>Parameters as configured; users of TD-SS-01</t>
         </is>
       </c>
       <c r="E12" s="12" t="n">
@@ -28151,7 +27233,7 @@
       </c>
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>Parameters and jobs as delivered</t>
+          <t>Parameters and jobs at their defaults</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
@@ -28161,7 +27243,7 @@
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>Configuration delivered with the build (FRS section 9.1); recipients set by the test lead</t>
+          <t>Configuration of the SIT environment (FRS section 9.1); recipients set by the test lead</t>
         </is>
       </c>
       <c r="E14" s="12" t="n">
@@ -28198,7 +27280,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M68"/>
+  <dimension ref="A1:L68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -28208,12 +27290,11 @@
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="28" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -28243,7 +27324,6 @@
       <c r="J3" s="25" t="n"/>
       <c r="K3" s="25" t="n"/>
       <c r="L3" s="25" t="n"/>
-      <c r="M3" s="25" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="26" t="inlineStr">
@@ -28283,32 +27363,27 @@
       </c>
       <c r="H4" s="26" t="inlineStr">
         <is>
-          <t>Automation reference</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="I4" s="26" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Actual result</t>
         </is>
       </c>
       <c r="J4" s="26" t="inlineStr">
         <is>
-          <t>Actual result</t>
+          <t>Tester</t>
         </is>
       </c>
       <c r="K4" s="26" t="inlineStr">
         <is>
-          <t>Tester</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="L4" s="26" t="inlineStr">
         <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="M4" s="26" t="inlineStr">
-        <is>
-          <t>Defect ID</t>
+          <t>Issue ID</t>
         </is>
       </c>
     </row>
@@ -28348,16 +27423,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H5" s="12" t="inlineStr"/>
-      <c r="I5" s="27" t="inlineStr">
+      <c r="H5" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I5" s="12" t="n"/>
       <c r="J5" s="12" t="n"/>
-      <c r="K5" s="12" t="n"/>
-      <c r="L5" s="28" t="n"/>
-      <c r="M5" s="12" t="n"/>
+      <c r="K5" s="28" t="n"/>
+      <c r="L5" s="12" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
@@ -28395,16 +27469,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H6" s="12" t="inlineStr"/>
-      <c r="I6" s="27" t="inlineStr">
+      <c r="H6" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I6" s="12" t="n"/>
       <c r="J6" s="12" t="n"/>
-      <c r="K6" s="12" t="n"/>
-      <c r="L6" s="28" t="n"/>
-      <c r="M6" s="12" t="n"/>
+      <c r="K6" s="28" t="n"/>
+      <c r="L6" s="12" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
@@ -28442,16 +27515,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H7" s="12" t="inlineStr"/>
-      <c r="I7" s="27" t="inlineStr">
+      <c r="H7" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I7" s="12" t="n"/>
       <c r="J7" s="12" t="n"/>
-      <c r="K7" s="12" t="n"/>
-      <c r="L7" s="28" t="n"/>
-      <c r="M7" s="12" t="n"/>
+      <c r="K7" s="28" t="n"/>
+      <c r="L7" s="12" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
@@ -28489,16 +27561,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H8" s="12" t="inlineStr"/>
-      <c r="I8" s="27" t="inlineStr">
+      <c r="H8" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I8" s="12" t="n"/>
       <c r="J8" s="12" t="n"/>
-      <c r="K8" s="12" t="n"/>
-      <c r="L8" s="28" t="n"/>
-      <c r="M8" s="12" t="n"/>
+      <c r="K8" s="28" t="n"/>
+      <c r="L8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
@@ -28536,16 +27607,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H9" s="12" t="inlineStr"/>
-      <c r="I9" s="27" t="inlineStr">
+      <c r="H9" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I9" s="12" t="n"/>
       <c r="J9" s="12" t="n"/>
-      <c r="K9" s="12" t="n"/>
-      <c r="L9" s="28" t="n"/>
-      <c r="M9" s="12" t="n"/>
+      <c r="K9" s="28" t="n"/>
+      <c r="L9" s="12" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
@@ -28583,16 +27653,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H10" s="12" t="inlineStr"/>
-      <c r="I10" s="27" t="inlineStr">
+      <c r="H10" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I10" s="12" t="n"/>
       <c r="J10" s="12" t="n"/>
-      <c r="K10" s="12" t="n"/>
-      <c r="L10" s="28" t="n"/>
-      <c r="M10" s="12" t="n"/>
+      <c r="K10" s="28" t="n"/>
+      <c r="L10" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
@@ -28630,16 +27699,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H11" s="12" t="inlineStr"/>
-      <c r="I11" s="27" t="inlineStr">
+      <c r="H11" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I11" s="12" t="n"/>
       <c r="J11" s="12" t="n"/>
-      <c r="K11" s="12" t="n"/>
-      <c r="L11" s="28" t="n"/>
-      <c r="M11" s="12" t="n"/>
+      <c r="K11" s="28" t="n"/>
+      <c r="L11" s="12" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
@@ -28677,16 +27745,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H12" s="12" t="inlineStr"/>
-      <c r="I12" s="27" t="inlineStr">
+      <c r="H12" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I12" s="12" t="n"/>
       <c r="J12" s="12" t="n"/>
-      <c r="K12" s="12" t="n"/>
-      <c r="L12" s="28" t="n"/>
-      <c r="M12" s="12" t="n"/>
+      <c r="K12" s="28" t="n"/>
+      <c r="L12" s="12" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
@@ -28724,16 +27791,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H13" s="12" t="inlineStr"/>
-      <c r="I13" s="27" t="inlineStr">
+      <c r="H13" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I13" s="12" t="n"/>
       <c r="J13" s="12" t="n"/>
-      <c r="K13" s="12" t="n"/>
-      <c r="L13" s="28" t="n"/>
-      <c r="M13" s="12" t="n"/>
+      <c r="K13" s="28" t="n"/>
+      <c r="L13" s="12" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
@@ -28768,19 +27834,18 @@
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
-          <t>Sanction Screening is not in the menu; /screening shows the no-access page.</t>
-        </is>
-      </c>
-      <c r="H14" s="12" t="inlineStr"/>
-      <c r="I14" s="27" t="inlineStr">
+          <t>Sanction Screening is not in the menu; its address shows the no-access page.</t>
+        </is>
+      </c>
+      <c r="H14" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I14" s="12" t="n"/>
       <c r="J14" s="12" t="n"/>
-      <c r="K14" s="12" t="n"/>
-      <c r="L14" s="28" t="n"/>
-      <c r="M14" s="12" t="n"/>
+      <c r="K14" s="28" t="n"/>
+      <c r="L14" s="12" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
@@ -28818,16 +27883,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H15" s="12" t="inlineStr"/>
-      <c r="I15" s="27" t="inlineStr">
+      <c r="H15" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I15" s="12" t="n"/>
       <c r="J15" s="12" t="n"/>
-      <c r="K15" s="12" t="n"/>
-      <c r="L15" s="28" t="n"/>
-      <c r="M15" s="12" t="n"/>
+      <c r="K15" s="28" t="n"/>
+      <c r="L15" s="12" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
@@ -28862,19 +27926,18 @@
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
-          <t>New Draft and Submit for Approval are not shown; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H16" s="12" t="inlineStr"/>
-      <c r="I16" s="27" t="inlineStr">
+          <t>New Draft and Submit for Approval are not shown; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H16" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I16" s="12" t="n"/>
       <c r="J16" s="12" t="n"/>
-      <c r="K16" s="12" t="n"/>
-      <c r="L16" s="28" t="n"/>
-      <c r="M16" s="12" t="n"/>
+      <c r="K16" s="28" t="n"/>
+      <c r="L16" s="12" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
@@ -28909,19 +27972,18 @@
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
-          <t>New Draft and Submit for Approval are not shown; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H17" s="12" t="inlineStr"/>
-      <c r="I17" s="27" t="inlineStr">
+          <t>New Draft and Submit for Approval are not shown; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H17" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I17" s="12" t="n"/>
       <c r="J17" s="12" t="n"/>
-      <c r="K17" s="12" t="n"/>
-      <c r="L17" s="28" t="n"/>
-      <c r="M17" s="12" t="n"/>
+      <c r="K17" s="28" t="n"/>
+      <c r="L17" s="12" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
@@ -28956,19 +28018,18 @@
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
-          <t>New Draft and Submit for Approval are not shown; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H18" s="12" t="inlineStr"/>
-      <c r="I18" s="27" t="inlineStr">
+          <t>New Draft and Submit for Approval are not shown; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H18" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I18" s="12" t="n"/>
       <c r="J18" s="12" t="n"/>
-      <c r="K18" s="12" t="n"/>
-      <c r="L18" s="28" t="n"/>
-      <c r="M18" s="12" t="n"/>
+      <c r="K18" s="28" t="n"/>
+      <c r="L18" s="12" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
@@ -29003,19 +28064,18 @@
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
-          <t>New Draft and Submit for Approval are not shown; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H19" s="12" t="inlineStr"/>
-      <c r="I19" s="27" t="inlineStr">
+          <t>New Draft and Submit for Approval are not shown; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H19" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I19" s="12" t="n"/>
       <c r="J19" s="12" t="n"/>
-      <c r="K19" s="12" t="n"/>
-      <c r="L19" s="28" t="n"/>
-      <c r="M19" s="12" t="n"/>
+      <c r="K19" s="28" t="n"/>
+      <c r="L19" s="12" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
@@ -29053,16 +28113,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H20" s="12" t="inlineStr"/>
-      <c r="I20" s="27" t="inlineStr">
+      <c r="H20" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I20" s="12" t="n"/>
       <c r="J20" s="12" t="n"/>
-      <c r="K20" s="12" t="n"/>
-      <c r="L20" s="28" t="n"/>
-      <c r="M20" s="12" t="n"/>
+      <c r="K20" s="28" t="n"/>
+      <c r="L20" s="12" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
@@ -29097,19 +28156,18 @@
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
-          <t>Approve and Reject are not shown; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H21" s="12" t="inlineStr"/>
-      <c r="I21" s="27" t="inlineStr">
+          <t>Approve and Reject are not shown; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H21" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I21" s="12" t="n"/>
       <c r="J21" s="12" t="n"/>
-      <c r="K21" s="12" t="n"/>
-      <c r="L21" s="28" t="n"/>
-      <c r="M21" s="12" t="n"/>
+      <c r="K21" s="28" t="n"/>
+      <c r="L21" s="12" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
@@ -29144,19 +28202,18 @@
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
-          <t>Approve and Reject are not shown; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H22" s="12" t="inlineStr"/>
-      <c r="I22" s="27" t="inlineStr">
+          <t>Approve and Reject are not shown; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H22" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I22" s="12" t="n"/>
       <c r="J22" s="12" t="n"/>
-      <c r="K22" s="12" t="n"/>
-      <c r="L22" s="28" t="n"/>
-      <c r="M22" s="12" t="n"/>
+      <c r="K22" s="28" t="n"/>
+      <c r="L22" s="12" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
@@ -29194,16 +28251,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H23" s="12" t="inlineStr"/>
-      <c r="I23" s="27" t="inlineStr">
+      <c r="H23" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I23" s="12" t="n"/>
       <c r="J23" s="12" t="n"/>
-      <c r="K23" s="12" t="n"/>
-      <c r="L23" s="28" t="n"/>
-      <c r="M23" s="12" t="n"/>
+      <c r="K23" s="28" t="n"/>
+      <c r="L23" s="12" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
@@ -29238,19 +28294,18 @@
       </c>
       <c r="G24" s="12" t="inlineStr">
         <is>
-          <t>Add Entry and Upload List File are not shown; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H24" s="12" t="inlineStr"/>
-      <c r="I24" s="27" t="inlineStr">
+          <t>Add Entry and Upload List File are not shown; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H24" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I24" s="12" t="n"/>
       <c r="J24" s="12" t="n"/>
-      <c r="K24" s="12" t="n"/>
-      <c r="L24" s="28" t="n"/>
-      <c r="M24" s="12" t="n"/>
+      <c r="K24" s="28" t="n"/>
+      <c r="L24" s="12" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
@@ -29285,19 +28340,18 @@
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
-          <t>Add Entry and Upload List File are not shown; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H25" s="12" t="inlineStr"/>
-      <c r="I25" s="27" t="inlineStr">
+          <t>Add Entry and Upload List File are not shown; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H25" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I25" s="12" t="n"/>
       <c r="J25" s="12" t="n"/>
-      <c r="K25" s="12" t="n"/>
-      <c r="L25" s="28" t="n"/>
-      <c r="M25" s="12" t="n"/>
+      <c r="K25" s="28" t="n"/>
+      <c r="L25" s="12" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
@@ -29332,19 +28386,18 @@
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
-          <t>Add Entry and Upload List File are not shown; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H26" s="12" t="inlineStr"/>
-      <c r="I26" s="27" t="inlineStr">
+          <t>Add Entry and Upload List File are not shown; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H26" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I26" s="12" t="n"/>
       <c r="J26" s="12" t="n"/>
-      <c r="K26" s="12" t="n"/>
-      <c r="L26" s="28" t="n"/>
-      <c r="M26" s="12" t="n"/>
+      <c r="K26" s="28" t="n"/>
+      <c r="L26" s="12" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
@@ -29382,16 +28435,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H27" s="12" t="inlineStr"/>
-      <c r="I27" s="27" t="inlineStr">
+      <c r="H27" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I27" s="12" t="n"/>
       <c r="J27" s="12" t="n"/>
-      <c r="K27" s="12" t="n"/>
-      <c r="L27" s="28" t="n"/>
-      <c r="M27" s="12" t="n"/>
+      <c r="K27" s="28" t="n"/>
+      <c r="L27" s="12" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
@@ -29426,19 +28478,18 @@
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
-          <t>The list change is not offered in My Approvals; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H28" s="12" t="inlineStr"/>
-      <c r="I28" s="27" t="inlineStr">
+          <t>The list change is not offered in My Approvals; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H28" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I28" s="12" t="n"/>
       <c r="J28" s="12" t="n"/>
-      <c r="K28" s="12" t="n"/>
-      <c r="L28" s="28" t="n"/>
-      <c r="M28" s="12" t="n"/>
+      <c r="K28" s="28" t="n"/>
+      <c r="L28" s="12" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
@@ -29473,19 +28524,18 @@
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
-          <t>The list change is not offered in My Approvals; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H29" s="12" t="inlineStr"/>
-      <c r="I29" s="27" t="inlineStr">
+          <t>The list change is not offered in My Approvals; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H29" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I29" s="12" t="n"/>
       <c r="J29" s="12" t="n"/>
-      <c r="K29" s="12" t="n"/>
-      <c r="L29" s="28" t="n"/>
-      <c r="M29" s="12" t="n"/>
+      <c r="K29" s="28" t="n"/>
+      <c r="L29" s="12" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
@@ -29523,16 +28573,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H30" s="12" t="inlineStr"/>
-      <c r="I30" s="27" t="inlineStr">
+      <c r="H30" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I30" s="12" t="n"/>
       <c r="J30" s="12" t="n"/>
-      <c r="K30" s="12" t="n"/>
-      <c r="L30" s="28" t="n"/>
-      <c r="M30" s="12" t="n"/>
+      <c r="K30" s="28" t="n"/>
+      <c r="L30" s="12" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
@@ -29570,16 +28619,15 @@
           <t>The Review tab is read only and Submit is not shown.</t>
         </is>
       </c>
-      <c r="H31" s="12" t="inlineStr"/>
-      <c r="I31" s="27" t="inlineStr">
+      <c r="H31" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I31" s="12" t="n"/>
       <c r="J31" s="12" t="n"/>
-      <c r="K31" s="12" t="n"/>
-      <c r="L31" s="28" t="n"/>
-      <c r="M31" s="12" t="n"/>
+      <c r="K31" s="28" t="n"/>
+      <c r="L31" s="12" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
@@ -29617,16 +28665,15 @@
           <t>The Review tab is read only and Submit is not shown.</t>
         </is>
       </c>
-      <c r="H32" s="12" t="inlineStr"/>
-      <c r="I32" s="27" t="inlineStr">
+      <c r="H32" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I32" s="12" t="n"/>
       <c r="J32" s="12" t="n"/>
-      <c r="K32" s="12" t="n"/>
-      <c r="L32" s="28" t="n"/>
-      <c r="M32" s="12" t="n"/>
+      <c r="K32" s="28" t="n"/>
+      <c r="L32" s="12" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
@@ -29664,16 +28711,15 @@
           <t>The Review tab is read only and Submit is not shown.</t>
         </is>
       </c>
-      <c r="H33" s="12" t="inlineStr"/>
-      <c r="I33" s="27" t="inlineStr">
+      <c r="H33" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I33" s="12" t="n"/>
       <c r="J33" s="12" t="n"/>
-      <c r="K33" s="12" t="n"/>
-      <c r="L33" s="28" t="n"/>
-      <c r="M33" s="12" t="n"/>
+      <c r="K33" s="28" t="n"/>
+      <c r="L33" s="12" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
@@ -29711,16 +28757,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H34" s="12" t="inlineStr"/>
-      <c r="I34" s="27" t="inlineStr">
+      <c r="H34" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I34" s="12" t="n"/>
       <c r="J34" s="12" t="n"/>
-      <c r="K34" s="12" t="n"/>
-      <c r="L34" s="28" t="n"/>
-      <c r="M34" s="12" t="n"/>
+      <c r="K34" s="28" t="n"/>
+      <c r="L34" s="12" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
@@ -29758,16 +28803,15 @@
           <t>Update Risk Tag and Mark False Positive are not shown.</t>
         </is>
       </c>
-      <c r="H35" s="12" t="inlineStr"/>
-      <c r="I35" s="27" t="inlineStr">
+      <c r="H35" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I35" s="12" t="n"/>
       <c r="J35" s="12" t="n"/>
-      <c r="K35" s="12" t="n"/>
-      <c r="L35" s="28" t="n"/>
-      <c r="M35" s="12" t="n"/>
+      <c r="K35" s="28" t="n"/>
+      <c r="L35" s="12" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
@@ -29805,16 +28849,15 @@
           <t>Update Risk Tag and Mark False Positive are not shown.</t>
         </is>
       </c>
-      <c r="H36" s="12" t="inlineStr"/>
-      <c r="I36" s="27" t="inlineStr">
+      <c r="H36" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I36" s="12" t="n"/>
       <c r="J36" s="12" t="n"/>
-      <c r="K36" s="12" t="n"/>
-      <c r="L36" s="28" t="n"/>
-      <c r="M36" s="12" t="n"/>
+      <c r="K36" s="28" t="n"/>
+      <c r="L36" s="12" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="12" t="inlineStr">
@@ -29852,16 +28895,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H37" s="12" t="inlineStr"/>
-      <c r="I37" s="27" t="inlineStr">
+      <c r="H37" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I37" s="12" t="n"/>
       <c r="J37" s="12" t="n"/>
-      <c r="K37" s="12" t="n"/>
-      <c r="L37" s="28" t="n"/>
-      <c r="M37" s="12" t="n"/>
+      <c r="K37" s="28" t="n"/>
+      <c r="L37" s="12" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="12" t="inlineStr">
@@ -29899,16 +28941,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H38" s="12" t="inlineStr"/>
-      <c r="I38" s="27" t="inlineStr">
+      <c r="H38" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I38" s="12" t="n"/>
       <c r="J38" s="12" t="n"/>
-      <c r="K38" s="12" t="n"/>
-      <c r="L38" s="28" t="n"/>
-      <c r="M38" s="12" t="n"/>
+      <c r="K38" s="28" t="n"/>
+      <c r="L38" s="12" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="12" t="inlineStr">
@@ -29946,16 +28987,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H39" s="12" t="inlineStr"/>
-      <c r="I39" s="27" t="inlineStr">
+      <c r="H39" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I39" s="12" t="n"/>
       <c r="J39" s="12" t="n"/>
-      <c r="K39" s="12" t="n"/>
-      <c r="L39" s="28" t="n"/>
-      <c r="M39" s="12" t="n"/>
+      <c r="K39" s="28" t="n"/>
+      <c r="L39" s="12" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="12" t="inlineStr">
@@ -29990,19 +29030,18 @@
       </c>
       <c r="G40" s="12" t="inlineStr">
         <is>
-          <t>Re-assign is not shown; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H40" s="12" t="inlineStr"/>
-      <c r="I40" s="27" t="inlineStr">
+          <t>Re-assign is not shown; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H40" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I40" s="12" t="n"/>
       <c r="J40" s="12" t="n"/>
-      <c r="K40" s="12" t="n"/>
-      <c r="L40" s="28" t="n"/>
-      <c r="M40" s="12" t="n"/>
+      <c r="K40" s="28" t="n"/>
+      <c r="L40" s="12" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
@@ -30037,19 +29076,18 @@
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
-          <t>Re-assign is not shown; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H41" s="12" t="inlineStr"/>
-      <c r="I41" s="27" t="inlineStr">
+          <t>Re-assign is not shown; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H41" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I41" s="12" t="n"/>
       <c r="J41" s="12" t="n"/>
-      <c r="K41" s="12" t="n"/>
-      <c r="L41" s="28" t="n"/>
-      <c r="M41" s="12" t="n"/>
+      <c r="K41" s="28" t="n"/>
+      <c r="L41" s="12" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="12" t="inlineStr">
@@ -30087,16 +29125,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H42" s="12" t="inlineStr"/>
-      <c r="I42" s="27" t="inlineStr">
+      <c r="H42" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I42" s="12" t="n"/>
       <c r="J42" s="12" t="n"/>
-      <c r="K42" s="12" t="n"/>
-      <c r="L42" s="28" t="n"/>
-      <c r="M42" s="12" t="n"/>
+      <c r="K42" s="28" t="n"/>
+      <c r="L42" s="12" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="12" t="inlineStr">
@@ -30131,19 +29168,18 @@
       </c>
       <c r="G43" s="12" t="inlineStr">
         <is>
-          <t>Approve and Disapprove are not shown; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H43" s="12" t="inlineStr"/>
-      <c r="I43" s="27" t="inlineStr">
+          <t>Approve and Disapprove are not shown; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H43" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I43" s="12" t="n"/>
       <c r="J43" s="12" t="n"/>
-      <c r="K43" s="12" t="n"/>
-      <c r="L43" s="28" t="n"/>
-      <c r="M43" s="12" t="n"/>
+      <c r="K43" s="28" t="n"/>
+      <c r="L43" s="12" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="12" t="inlineStr">
@@ -30178,19 +29214,18 @@
       </c>
       <c r="G44" s="12" t="inlineStr">
         <is>
-          <t>Approve and Disapprove are not shown; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H44" s="12" t="inlineStr"/>
-      <c r="I44" s="27" t="inlineStr">
+          <t>Approve and Disapprove are not shown; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H44" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I44" s="12" t="n"/>
       <c r="J44" s="12" t="n"/>
-      <c r="K44" s="12" t="n"/>
-      <c r="L44" s="28" t="n"/>
-      <c r="M44" s="12" t="n"/>
+      <c r="K44" s="28" t="n"/>
+      <c r="L44" s="12" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="12" t="inlineStr">
@@ -30228,16 +29263,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H45" s="12" t="inlineStr"/>
-      <c r="I45" s="27" t="inlineStr">
+      <c r="H45" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I45" s="12" t="n"/>
       <c r="J45" s="12" t="n"/>
-      <c r="K45" s="12" t="n"/>
-      <c r="L45" s="28" t="n"/>
-      <c r="M45" s="12" t="n"/>
+      <c r="K45" s="28" t="n"/>
+      <c r="L45" s="12" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="12" t="inlineStr">
@@ -30272,19 +29306,18 @@
       </c>
       <c r="G46" s="12" t="inlineStr">
         <is>
-          <t>The outcome list and the STR tab actions are not shown; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H46" s="12" t="inlineStr"/>
-      <c r="I46" s="27" t="inlineStr">
+          <t>The outcome list and the STR tab actions are not shown; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H46" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I46" s="12" t="n"/>
       <c r="J46" s="12" t="n"/>
-      <c r="K46" s="12" t="n"/>
-      <c r="L46" s="28" t="n"/>
-      <c r="M46" s="12" t="n"/>
+      <c r="K46" s="28" t="n"/>
+      <c r="L46" s="12" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="12" t="inlineStr">
@@ -30319,19 +29352,18 @@
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
-          <t>The outcome list and the STR tab actions are not shown; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H47" s="12" t="inlineStr"/>
-      <c r="I47" s="27" t="inlineStr">
+          <t>The outcome list and the STR tab actions are not shown; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H47" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I47" s="12" t="n"/>
       <c r="J47" s="12" t="n"/>
-      <c r="K47" s="12" t="n"/>
-      <c r="L47" s="28" t="n"/>
-      <c r="M47" s="12" t="n"/>
+      <c r="K47" s="28" t="n"/>
+      <c r="L47" s="12" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="12" t="inlineStr">
@@ -30366,19 +29398,18 @@
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
-          <t>The outcome list and the STR tab actions are not shown; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H48" s="12" t="inlineStr"/>
-      <c r="I48" s="27" t="inlineStr">
+          <t>The outcome list and the STR tab actions are not shown; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H48" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I48" s="12" t="n"/>
       <c r="J48" s="12" t="n"/>
-      <c r="K48" s="12" t="n"/>
-      <c r="L48" s="28" t="n"/>
-      <c r="M48" s="12" t="n"/>
+      <c r="K48" s="28" t="n"/>
+      <c r="L48" s="12" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="12" t="inlineStr">
@@ -30416,16 +29447,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H49" s="12" t="inlineStr"/>
-      <c r="I49" s="27" t="inlineStr">
+      <c r="H49" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I49" s="12" t="n"/>
       <c r="J49" s="12" t="n"/>
-      <c r="K49" s="12" t="n"/>
-      <c r="L49" s="28" t="n"/>
-      <c r="M49" s="12" t="n"/>
+      <c r="K49" s="28" t="n"/>
+      <c r="L49" s="12" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="12" t="inlineStr">
@@ -30460,19 +29490,18 @@
       </c>
       <c r="G50" s="12" t="inlineStr">
         <is>
-          <t>Record Decision is not shown; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H50" s="12" t="inlineStr"/>
-      <c r="I50" s="27" t="inlineStr">
+          <t>Record Decision is not shown; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H50" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I50" s="12" t="n"/>
       <c r="J50" s="12" t="n"/>
-      <c r="K50" s="12" t="n"/>
-      <c r="L50" s="28" t="n"/>
-      <c r="M50" s="12" t="n"/>
+      <c r="K50" s="28" t="n"/>
+      <c r="L50" s="12" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
@@ -30507,19 +29536,18 @@
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>
-          <t>Record Decision is not shown; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H51" s="12" t="inlineStr"/>
-      <c r="I51" s="27" t="inlineStr">
+          <t>Record Decision is not shown; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H51" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I51" s="12" t="n"/>
       <c r="J51" s="12" t="n"/>
-      <c r="K51" s="12" t="n"/>
-      <c r="L51" s="28" t="n"/>
-      <c r="M51" s="12" t="n"/>
+      <c r="K51" s="28" t="n"/>
+      <c r="L51" s="12" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="12" t="inlineStr">
@@ -30554,19 +29582,18 @@
       </c>
       <c r="G52" s="12" t="inlineStr">
         <is>
-          <t>Record Decision is not shown; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H52" s="12" t="inlineStr"/>
-      <c r="I52" s="27" t="inlineStr">
+          <t>Record Decision is not shown; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H52" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I52" s="12" t="n"/>
       <c r="J52" s="12" t="n"/>
-      <c r="K52" s="12" t="n"/>
-      <c r="L52" s="28" t="n"/>
-      <c r="M52" s="12" t="n"/>
+      <c r="K52" s="28" t="n"/>
+      <c r="L52" s="12" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="12" t="inlineStr">
@@ -30604,16 +29631,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H53" s="12" t="inlineStr"/>
-      <c r="I53" s="27" t="inlineStr">
+      <c r="H53" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I53" s="12" t="n"/>
       <c r="J53" s="12" t="n"/>
-      <c r="K53" s="12" t="n"/>
-      <c r="L53" s="28" t="n"/>
-      <c r="M53" s="12" t="n"/>
+      <c r="K53" s="28" t="n"/>
+      <c r="L53" s="12" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="12" t="inlineStr">
@@ -30648,19 +29674,18 @@
       </c>
       <c r="G54" s="12" t="inlineStr">
         <is>
-          <t>Extract Approved STRs and Record Filing are not shown; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H54" s="12" t="inlineStr"/>
-      <c r="I54" s="27" t="inlineStr">
+          <t>Extract Approved STRs and Record Filing are not shown; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H54" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I54" s="12" t="n"/>
       <c r="J54" s="12" t="n"/>
-      <c r="K54" s="12" t="n"/>
-      <c r="L54" s="28" t="n"/>
-      <c r="M54" s="12" t="n"/>
+      <c r="K54" s="28" t="n"/>
+      <c r="L54" s="12" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="12" t="inlineStr">
@@ -30695,19 +29720,18 @@
       </c>
       <c r="G55" s="12" t="inlineStr">
         <is>
-          <t>Extract Approved STRs and Record Filing are not shown; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H55" s="12" t="inlineStr"/>
-      <c r="I55" s="27" t="inlineStr">
+          <t>Extract Approved STRs and Record Filing are not shown; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H55" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I55" s="12" t="n"/>
       <c r="J55" s="12" t="n"/>
-      <c r="K55" s="12" t="n"/>
-      <c r="L55" s="28" t="n"/>
-      <c r="M55" s="12" t="n"/>
+      <c r="K55" s="28" t="n"/>
+      <c r="L55" s="12" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="12" t="inlineStr">
@@ -30745,16 +29769,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H56" s="12" t="inlineStr"/>
-      <c r="I56" s="27" t="inlineStr">
+      <c r="H56" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I56" s="12" t="n"/>
       <c r="J56" s="12" t="n"/>
-      <c r="K56" s="12" t="n"/>
-      <c r="L56" s="28" t="n"/>
-      <c r="M56" s="12" t="n"/>
+      <c r="K56" s="28" t="n"/>
+      <c r="L56" s="12" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="12" t="inlineStr">
@@ -30792,16 +29815,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H57" s="12" t="inlineStr"/>
-      <c r="I57" s="27" t="inlineStr">
+      <c r="H57" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I57" s="12" t="n"/>
       <c r="J57" s="12" t="n"/>
-      <c r="K57" s="12" t="n"/>
-      <c r="L57" s="28" t="n"/>
-      <c r="M57" s="12" t="n"/>
+      <c r="K57" s="28" t="n"/>
+      <c r="L57" s="12" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="12" t="inlineStr">
@@ -30839,16 +29861,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H58" s="12" t="inlineStr"/>
-      <c r="I58" s="27" t="inlineStr">
+      <c r="H58" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I58" s="12" t="n"/>
       <c r="J58" s="12" t="n"/>
-      <c r="K58" s="12" t="n"/>
-      <c r="L58" s="28" t="n"/>
-      <c r="M58" s="12" t="n"/>
+      <c r="K58" s="28" t="n"/>
+      <c r="L58" s="12" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="12" t="inlineStr">
@@ -30886,16 +29907,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H59" s="12" t="inlineStr"/>
-      <c r="I59" s="27" t="inlineStr">
+      <c r="H59" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I59" s="12" t="n"/>
       <c r="J59" s="12" t="n"/>
-      <c r="K59" s="12" t="n"/>
-      <c r="L59" s="28" t="n"/>
-      <c r="M59" s="12" t="n"/>
+      <c r="K59" s="28" t="n"/>
+      <c r="L59" s="12" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="12" t="inlineStr">
@@ -30933,16 +29953,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H60" s="12" t="inlineStr"/>
-      <c r="I60" s="27" t="inlineStr">
+      <c r="H60" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I60" s="12" t="n"/>
       <c r="J60" s="12" t="n"/>
-      <c r="K60" s="12" t="n"/>
-      <c r="L60" s="28" t="n"/>
-      <c r="M60" s="12" t="n"/>
+      <c r="K60" s="28" t="n"/>
+      <c r="L60" s="12" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="12" t="inlineStr">
@@ -30977,19 +29996,18 @@
       </c>
       <c r="G61" s="12" t="inlineStr">
         <is>
-          <t>The Compliance category is not listed; the run call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H61" s="12" t="inlineStr"/>
-      <c r="I61" s="27" t="inlineStr">
+          <t>The Compliance category is not listed; a direct run request is refused.</t>
+        </is>
+      </c>
+      <c r="H61" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I61" s="12" t="n"/>
       <c r="J61" s="12" t="n"/>
-      <c r="K61" s="12" t="n"/>
-      <c r="L61" s="28" t="n"/>
-      <c r="M61" s="12" t="n"/>
+      <c r="K61" s="28" t="n"/>
+      <c r="L61" s="12" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="12" t="inlineStr">
@@ -31024,19 +30042,18 @@
       </c>
       <c r="G62" s="12" t="inlineStr">
         <is>
-          <t>The Compliance category is not listed; the run call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H62" s="12" t="inlineStr"/>
-      <c r="I62" s="27" t="inlineStr">
+          <t>The Compliance category is not listed; a direct run request is refused.</t>
+        </is>
+      </c>
+      <c r="H62" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I62" s="12" t="n"/>
       <c r="J62" s="12" t="n"/>
-      <c r="K62" s="12" t="n"/>
-      <c r="L62" s="28" t="n"/>
-      <c r="M62" s="12" t="n"/>
+      <c r="K62" s="28" t="n"/>
+      <c r="L62" s="12" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="12" t="inlineStr">
@@ -31071,19 +30088,18 @@
       </c>
       <c r="G63" s="12" t="inlineStr">
         <is>
-          <t>The Compliance category is not listed; the run call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H63" s="12" t="inlineStr"/>
-      <c r="I63" s="27" t="inlineStr">
+          <t>The Compliance category is not listed; a direct run request is refused.</t>
+        </is>
+      </c>
+      <c r="H63" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I63" s="12" t="n"/>
       <c r="J63" s="12" t="n"/>
-      <c r="K63" s="12" t="n"/>
-      <c r="L63" s="28" t="n"/>
-      <c r="M63" s="12" t="n"/>
+      <c r="K63" s="28" t="n"/>
+      <c r="L63" s="12" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="12" t="inlineStr">
@@ -31121,16 +30137,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H64" s="12" t="inlineStr"/>
-      <c r="I64" s="27" t="inlineStr">
+      <c r="H64" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I64" s="12" t="n"/>
       <c r="J64" s="12" t="n"/>
-      <c r="K64" s="12" t="n"/>
-      <c r="L64" s="28" t="n"/>
-      <c r="M64" s="12" t="n"/>
+      <c r="K64" s="28" t="n"/>
+      <c r="L64" s="12" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="12" t="inlineStr">
@@ -31168,16 +30183,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H65" s="12" t="inlineStr"/>
-      <c r="I65" s="27" t="inlineStr">
+      <c r="H65" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I65" s="12" t="n"/>
       <c r="J65" s="12" t="n"/>
-      <c r="K65" s="12" t="n"/>
-      <c r="L65" s="28" t="n"/>
-      <c r="M65" s="12" t="n"/>
+      <c r="K65" s="28" t="n"/>
+      <c r="L65" s="12" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="12" t="inlineStr">
@@ -31212,19 +30226,18 @@
       </c>
       <c r="G66" s="12" t="inlineStr">
         <is>
-          <t>SCR-AUDIT-LOG is not listed; the run call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H66" s="12" t="inlineStr"/>
-      <c r="I66" s="27" t="inlineStr">
+          <t>SCR-AUDIT-LOG is not listed; a direct run request is refused.</t>
+        </is>
+      </c>
+      <c r="H66" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I66" s="12" t="n"/>
       <c r="J66" s="12" t="n"/>
-      <c r="K66" s="12" t="n"/>
-      <c r="L66" s="28" t="n"/>
-      <c r="M66" s="12" t="n"/>
+      <c r="K66" s="28" t="n"/>
+      <c r="L66" s="12" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="12" t="inlineStr">
@@ -31259,19 +30272,18 @@
       </c>
       <c r="G67" s="12" t="inlineStr">
         <is>
-          <t>SCR-AUDIT-LOG is not listed; the run call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H67" s="12" t="inlineStr"/>
-      <c r="I67" s="27" t="inlineStr">
+          <t>SCR-AUDIT-LOG is not listed; a direct run request is refused.</t>
+        </is>
+      </c>
+      <c r="H67" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I67" s="12" t="n"/>
       <c r="J67" s="12" t="n"/>
-      <c r="K67" s="12" t="n"/>
-      <c r="L67" s="28" t="n"/>
-      <c r="M67" s="12" t="n"/>
+      <c r="K67" s="28" t="n"/>
+      <c r="L67" s="12" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="12" t="inlineStr">
@@ -31306,26 +30318,25 @@
       </c>
       <c r="G68" s="12" t="inlineStr">
         <is>
-          <t>SCR-AUDIT-LOG is not listed; the run call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H68" s="12" t="inlineStr"/>
-      <c r="I68" s="27" t="inlineStr">
+          <t>SCR-AUDIT-LOG is not listed; a direct run request is refused.</t>
+        </is>
+      </c>
+      <c r="H68" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I68" s="12" t="n"/>
       <c r="J68" s="12" t="n"/>
-      <c r="K68" s="12" t="n"/>
-      <c r="L68" s="28" t="n"/>
-      <c r="M68" s="12" t="n"/>
+      <c r="K68" s="28" t="n"/>
+      <c r="L68" s="12" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:M68"/>
+  <autoFilter ref="A4:L68"/>
   <mergeCells count="1">
-    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A2:L2"/>
   </mergeCells>
-  <conditionalFormatting sqref="I5:I568">
+  <conditionalFormatting sqref="H5:H568">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="1" stopIfTrue="1">
       <formula>"Pass"</formula>
     </cfRule>
@@ -31339,7 +30350,7 @@
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A5:M568">
+  <conditionalFormatting sqref="A5:L568">
     <cfRule type="expression" priority="5" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>
@@ -31348,7 +30359,7 @@
     <dataValidation sqref="F5:F568" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Access" error="Choose a value from the list (Access)." type="list">
       <formula1>'_lists'!$F$1:$F$2</formula1>
     </dataValidation>
-    <dataValidation sqref="I5:I568" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Status" error="Choose a value from the list (Status)." type="list">
+    <dataValidation sqref="H5:H568" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Status" error="Choose a value from the list (Status)." type="list">
       <formula1>'_lists'!$G$1:$G$5</formula1>
     </dataValidation>
   </dataValidations>
